--- a/Group_Actions/Group_Actions_Test_Cases.xlsx
+++ b/Group_Actions/Group_Actions_Test_Cases.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2528,6 +2528,874 @@
       <c r="H55" s="2" t="inlineStr">
         <is>
           <t>High / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>GA_055</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Integration: Group Actions with Message List</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and group is open</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Verify adding member shows system message in chat</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>1. Add a new member to the group.
+2. Observe message list.</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>System message 'User X was added' should appear in the group chat.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>GA_056</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Verify kicking member shows system message in chat</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>1. Kick a member from the group.
+2. Observe message list.</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>System message 'User X was removed' should appear in the group chat.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>GA_057</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Integration: Group Actions with Conversation List</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Verify leaving group removes it from conversation list</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>1. Leave a group.
+2. Check conversation list.</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Group should be removed from conversation list (or marked as 'Left').</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>GA_058</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Integration: Group Actions with Notifications</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Verify group action triggers notification for affected members</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>1. Admin changes a member's scope.
+2. Check affected member's notifications.</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Affected member should receive notification about scope change.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>GA_059</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Regression: Group Actions</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and is group admin</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Verify group actions work after adding and removing same member</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>1. Add User X.
+2. Remove User X.
+3. Add User X again.</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>All actions should complete successfully. User X should be a member again.</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>GA_060</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Verify group actions after scope change</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>1. Change User X from member to admin.
+2. Perform admin actions as User X.</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>User X should have full admin capabilities after scope change.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>GA_061</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Verify member list accurate after multiple actions</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>1. Add 3 members, remove 1, ban 1.
+2. View member list.</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Member list should accurately reflect all changes. Counts should be correct.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>GA_062</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Security: Group Actions</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in as regular member</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Verify non-admin cannot add members</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as regular group member.
+2. Try to add a new member.</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Add member option should not be available or action should be rejected.</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>GA_063</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Verify non-admin cannot kick members</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as regular group member.
+2. Try to kick another member.</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Kick option should not be available or action should be rejected.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>GA_064</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr"/>
+      <c r="D65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Verify non-admin cannot ban members</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as regular group member.
+2. Try to ban another member.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Ban option should not be available or action should be rejected.</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>GA_065</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Verify non-admin cannot change member scope</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as regular group member.
+2. Try to change another member's scope.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Change scope option should not be available or action should be rejected.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>GA_066</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr"/>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in as group admin</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Verify admin cannot kick/ban the group owner</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>1. As admin, try to kick or ban the group owner.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Action should be blocked. Owner cannot be kicked or banned by admin.</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>GA_067</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>User is not a group member</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Verify non-member cannot access group actions</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to access group actions for a group you're not a member of.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Group actions should not be accessible. Appropriate error should display.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>GA_068</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case: Group Actions</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and is group admin</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Verify adding member to group at max member limit</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>1. Fill group to maximum member limit.
+2. Try to add one more member.</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Should show error that group is full. Member should not be added.</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>GA_069</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Verify banning all members except owner</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>1. Ban all members one by one (except owner).</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>All members should be banned. Group should still function with owner only.</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>GA_070</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr"/>
+      <c r="D71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Verify unbanning a previously banned member</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>1. Ban a member.
+2. Go to banned members list.
+3. Unban the member.</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Member should be unbanned and able to rejoin the group.</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>GA_071</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Verify group actions with 500+ members</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>1. Open group actions for a group with 500+ members.
+2. View member list.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Member list should load with pagination. Search should work. No performance issues.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>GA_072</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case: Group Actions</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Verify simultaneous admin actions on same member</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>1. Two admins try to kick the same member at the same time.</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>One action should succeed, the other should fail gracefully. No data corruption.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>GA_073</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Boundary: Group Actions</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and is group admin</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Verify group with exactly 2 members (minimum for group)</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>1. Have a group with exactly 2 members.
+2. Perform group actions.</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>All applicable actions should work. Leaving should handle last-member scenario.</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>GA_074</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr"/>
+      <c r="D75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Verify group with maximum allowed members</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>1. Fill group to max capacity.
+2. Verify all actions work.</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>All group actions should function correctly at max capacity.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>GA_075</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr"/>
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Verify banned members list with 0 banned members</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>1. Open banned members list when no one is banned.</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Empty state should display with appropriate message.</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>GA_076</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning: Member Scopes</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and is group owner</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Verify actions available for Owner scope</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as group owner.
+2. Observe available group actions.</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Owner should have all actions: add, kick, ban, change scope, delete group.</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>GA_077</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr"/>
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Verify actions available for Admin scope</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as group admin.
+2. Observe available group actions.</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Admin should have: add, kick (members only), ban (members only), change scope (members only).</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>GA_078</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr"/>
+      <c r="D79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Verify actions available for Moderator scope</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as group moderator.
+2. Observe available group actions.</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Moderator should have limited actions per role definition.</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>GA_079</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr"/>
+      <c r="D80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Verify actions available for Member scope</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as regular group member.
+2. Observe available group actions.</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Member should only have: leave group, view members. No admin actions.</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
         </is>
       </c>
     </row>

--- a/Group_Actions/Group_Actions_Test_Cases.xlsx
+++ b/Group_Actions/Group_Actions_Test_Cases.xlsx
@@ -7,7 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Group Actions Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Functional" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Integration" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Regression" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Security" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Edge Cases" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Boundary Values" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Equivalence Partitioning" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,6 +33,8 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -38,12 +46,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-        <bgColor rgb="00FFFF00"/>
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -57,32 +65,11 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -90,11 +77,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -457,23 +439,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
@@ -521,7 +504,7 @@
           <t>GA_001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -566,9 +549,9 @@
           <t>GA_002</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify group avatar display in info panel</t>
@@ -597,9 +580,9 @@
           <t>GA_003</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify group name display in info panel</t>
@@ -628,9 +611,9 @@
           <t>GA_004</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify member count in info panel</t>
@@ -659,9 +642,9 @@
           <t>GA_005</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify close button (X) functionality</t>
@@ -691,7 +674,7 @@
           <t>GA_006</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -734,9 +717,9 @@
           <t>GA_007</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="5" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Verify Add Members click opens dialog</t>
@@ -766,8 +749,8 @@
           <t>GA_008</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
           <t>User is logged in and Add Members dialog is open</t>
@@ -802,7 +785,7 @@
           <t>GA_009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -845,8 +828,8 @@
           <t>GA_010</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
           <t>User is non-admin member</t>
@@ -881,7 +864,7 @@
           <t>GA_011</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -924,9 +907,9 @@
           <t>GA_012</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="5" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Verify Delete Chat click shows confirmation</t>
@@ -956,8 +939,8 @@
           <t>GA_013</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t>User is logged in and confirmation shown</t>
@@ -1035,7 +1018,7 @@
           <t>GA_015</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1078,9 +1061,9 @@
           <t>GA_016</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="5" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Verify Leave click shows confirmation</t>
@@ -1110,8 +1093,8 @@
           <t>GA_017</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
           <t>User is logged in and confirmation shown</t>
@@ -1190,7 +1173,7 @@
           <t>GA_019</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1233,9 +1216,9 @@
           <t>GA_020</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="5" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Verify Delete and Exit click shows confirmation</t>
@@ -1265,8 +1248,8 @@
           <t>GA_021</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
           <t>User is owner and confirmation shown</t>
@@ -1345,7 +1328,7 @@
           <t>GA_023</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1388,9 +1371,9 @@
           <t>GA_024</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="5" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Verify View Members tab shows member list</t>
@@ -1420,8 +1403,8 @@
           <t>GA_025</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
           <t>User is logged in and View Members is active</t>
@@ -1455,9 +1438,9 @@
           <t>GA_026</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Verify member name display</t>
@@ -1486,9 +1469,9 @@
           <t>GA_027</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Verify owner badge display</t>
@@ -1517,9 +1500,9 @@
           <t>GA_028</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Verify online status indicator</t>
@@ -1548,7 +1531,7 @@
           <t>GA_029</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1591,9 +1574,9 @@
           <t>GA_030</t>
         </is>
       </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="5" t="n"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Verify Banned Members tab click</t>
@@ -1623,8 +1606,8 @@
           <t>GA_031</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="inlineStr">
         <is>
           <t>User is admin and Banned Members is active</t>
@@ -1702,7 +1685,7 @@
           <t>GA_033</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1746,9 +1729,9 @@
           <t>GA_034</t>
         </is>
       </c>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="n"/>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Verify search by member name</t>
@@ -1778,9 +1761,9 @@
           <t>GA_035</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Verify search clears correctly</t>
@@ -1853,7 +1836,7 @@
           <t>GA_037</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1897,9 +1880,9 @@
           <t>GA_038</t>
         </is>
       </c>
-      <c r="B39" s="4" t="n"/>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="5" t="n"/>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Verify Kick click shows confirmation</t>
@@ -1929,8 +1912,8 @@
           <t>GA_039</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="n"/>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
           <t>User is admin and confirmation shown</t>
@@ -1965,7 +1948,7 @@
           <t>GA_040</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -2009,8 +1992,8 @@
           <t>GA_041</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
           <t>User is admin viewing owner</t>
@@ -2045,7 +2028,7 @@
           <t>GA_042</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -2089,9 +2072,9 @@
           <t>GA_043</t>
         </is>
       </c>
-      <c r="B44" s="4" t="n"/>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="5" t="n"/>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Verify Ban click shows confirmation</t>
@@ -2121,8 +2104,8 @@
           <t>GA_044</t>
         </is>
       </c>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="n"/>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
           <t>User is admin and confirmation shown</t>
@@ -2157,7 +2140,7 @@
           <t>GA_045</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -2201,8 +2184,8 @@
           <t>GA_046</t>
         </is>
       </c>
-      <c r="B47" s="5" t="n"/>
-      <c r="C47" s="5" t="n"/>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="inlineStr">
         <is>
           <t>User is admin viewing owner</t>
@@ -2237,7 +2220,7 @@
           <t>GA_047</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -2281,9 +2264,9 @@
           <t>GA_048</t>
         </is>
       </c>
-      <c r="B49" s="4" t="n"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="5" t="n"/>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Verify Change Scope click opens options</t>
@@ -2313,8 +2296,8 @@
           <t>GA_049</t>
         </is>
       </c>
-      <c r="B50" s="4" t="n"/>
-      <c r="C50" s="4" t="n"/>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="inlineStr">
         <is>
           <t>User is admin and scope options shown</t>
@@ -2349,9 +2332,9 @@
           <t>GA_050</t>
         </is>
       </c>
-      <c r="B51" s="5" t="n"/>
-      <c r="C51" s="5" t="n"/>
-      <c r="D51" s="5" t="n"/>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Verify demoting admin to member</t>
@@ -2381,7 +2364,7 @@
           <t>GA_051</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -2425,8 +2408,8 @@
           <t>GA_052</t>
         </is>
       </c>
-      <c r="B53" s="5" t="n"/>
-      <c r="C53" s="5" t="n"/>
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="inlineStr">
         <is>
           <t>User is admin viewing owner</t>
@@ -2461,7 +2444,7 @@
           <t>GA_053</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -2505,9 +2488,9 @@
           <t>GA_054</t>
         </is>
       </c>
-      <c r="B55" s="5" t="n"/>
-      <c r="C55" s="5" t="n"/>
-      <c r="D55" s="5" t="n"/>
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Verify Group Info panel on mobile</t>
@@ -2531,923 +2514,1277 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>GA_055</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Integration: Group Actions with Message List</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in and group is open</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify adding member shows system message in chat</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Add a new member to the group.
 2. Observe message list.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>System message 'User X was added' should appear in the group chat.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>GA_056</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr"/>
-      <c r="C57" s="2" t="inlineStr"/>
-      <c r="D57" s="2" t="inlineStr"/>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify kicking member shows system message in chat</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Kick a member from the group.
 2. Observe message list.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>System message 'User X was removed' should appear in the group chat.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>GA_057</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr"/>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Integration: Group Actions with Conversation List</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr"/>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify leaving group removes it from conversation list</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Leave a group.
 2. Check conversation list.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Group should be removed from conversation list (or marked as 'Left').</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>GA_058</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr"/>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Integration: Group Actions with Notifications</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr"/>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify group action triggers notification for affected members</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Admin changes a member's scope.
 2. Check affected member's notifications.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Affected member should receive notification about scope change.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FFC000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>GA_059</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Regression: Group Actions</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in and is group admin</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify group actions work after adding and removing same member</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Add User X.
 2. Remove User X.
 3. Add User X again.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>All actions should complete successfully. User X should be a member again.</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>GA_060</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr"/>
-      <c r="C61" s="2" t="inlineStr"/>
-      <c r="D61" s="2" t="inlineStr"/>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify group actions after scope change</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Change User X from member to admin.
 2. Perform admin actions as User X.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>User X should have full admin capabilities after scope change.</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>GA_061</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr"/>
-      <c r="C62" s="2" t="inlineStr"/>
-      <c r="D62" s="2" t="inlineStr"/>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify member list accurate after multiple actions</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Add 3 members, remove 1, ban 1.
 2. View member list.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Member list should accurately reflect all changes. Counts should be correct.</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FF0000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>GA_062</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Security: Group Actions</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in as regular member</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify non-admin cannot add members</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Login as regular group member.
 2. Try to add a new member.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Add member option should not be available or action should be rejected.</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>GA_063</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr"/>
-      <c r="C64" s="2" t="inlineStr"/>
-      <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify non-admin cannot kick members</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Login as regular group member.
 2. Try to kick another member.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Kick option should not be available or action should be rejected.</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>GA_064</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr"/>
-      <c r="C65" s="2" t="inlineStr"/>
-      <c r="D65" s="2" t="inlineStr"/>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify non-admin cannot ban members</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Login as regular group member.
 2. Try to ban another member.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Ban option should not be available or action should be rejected.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>GA_065</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr"/>
-      <c r="C66" s="2" t="inlineStr"/>
-      <c r="D66" s="2" t="inlineStr"/>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify non-admin cannot change member scope</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Login as regular group member.
 2. Try to change another member's scope.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Change scope option should not be available or action should be rejected.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>GA_066</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr"/>
-      <c r="C67" s="2" t="inlineStr"/>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>User is logged in as group admin</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify admin cannot kick/ban the group owner</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>1. As admin, try to kick or ban the group owner.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Action should be blocked. Owner cannot be kicked or banned by admin.</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>GA_067</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr"/>
-      <c r="C68" s="2" t="inlineStr"/>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>User is not a group member</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Verify non-member cannot access group actions</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1. Try to access group actions for a group you're not a member of.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Group actions should not be accessible. Appropriate error should display.</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>GA_068</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Edge Case: Group Actions</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in and is group admin</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify adding member to group at max member limit</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Fill group to maximum member limit.
 2. Try to add one more member.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Should show error that group is full. Member should not be added.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>GA_069</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr"/>
-      <c r="C70" s="2" t="inlineStr"/>
-      <c r="D70" s="2" t="inlineStr"/>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify banning all members except owner</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Ban all members one by one (except owner).</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>All members should be banned. Group should still function with owner only.</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>GA_070</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr"/>
-      <c r="C71" s="2" t="inlineStr"/>
-      <c r="D71" s="2" t="inlineStr"/>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify unbanning a previously banned member</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Ban a member.
 2. Go to banned members list.
 3. Unban the member.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Member should be unbanned and able to rejoin the group.</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>GA_071</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr"/>
-      <c r="C72" s="2" t="inlineStr"/>
-      <c r="D72" s="2" t="inlineStr"/>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify group actions with 500+ members</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Open group actions for a group with 500+ members.
 2. View member list.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Member list should load with pagination. Search should work. No performance issues.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>GA_072</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Edge Case: Group Actions</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr"/>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify simultaneous admin actions on same member</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>1. Two admins try to kick the same member at the same time.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>One action should succeed, the other should fail gracefully. No data corruption.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>GA_073</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Boundary: Group Actions</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in and is group admin</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify group with exactly 2 members (minimum for group)</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Have a group with exactly 2 members.
 2. Perform group actions.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>All applicable actions should work. Leaving should handle last-member scenario.</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>GA_074</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr"/>
-      <c r="C75" s="2" t="inlineStr"/>
-      <c r="D75" s="2" t="inlineStr"/>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify group with maximum allowed members</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Fill group to max capacity.
 2. Verify all actions work.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>All group actions should function correctly at max capacity.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>GA_075</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr"/>
-      <c r="C76" s="2" t="inlineStr"/>
-      <c r="D76" s="2" t="inlineStr"/>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify banned members list with 0 banned members</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Open banned members list when no one is banned.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Empty state should display with appropriate message.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0000B0F0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>GA_076</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Member Scopes</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in and is group owner</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify actions available for Owner scope</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Login as group owner.
 2. Observe available group actions.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Owner should have all actions: add, kick, ban, change scope, delete group.</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>GA_077</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr"/>
-      <c r="C78" s="2" t="inlineStr"/>
-      <c r="D78" s="2" t="inlineStr"/>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify actions available for Admin scope</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Login as group admin.
 2. Observe available group actions.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Admin should have: add, kick (members only), ban (members only), change scope (members only).</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>GA_078</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr"/>
-      <c r="C79" s="2" t="inlineStr"/>
-      <c r="D79" s="2" t="inlineStr"/>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify actions available for Moderator scope</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Login as group moderator.
 2. Observe available group actions.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Moderator should have limited actions per role definition.</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>GA_079</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr"/>
-      <c r="C80" s="2" t="inlineStr"/>
-      <c r="D80" s="2" t="inlineStr"/>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify actions available for Member scope</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Login as regular group member.
 2. Observe available group actions.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Member should only have: leave group, view members. No admin actions.</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="46">
-    <mergeCell ref="C2:C6"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C24:C29"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="B48:B51"/>
-    <mergeCell ref="D24:D25"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="D34:D36"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="B24:B29"/>
-    <mergeCell ref="D54:D55"/>
-    <mergeCell ref="D2:D6"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="C48:C51"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D26:D29"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B38:B40"/>
-    <mergeCell ref="D50:D51"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Group_Actions/Group_Actions_Test_Cases.xlsx
+++ b/Group_Actions/Group_Actions_Test_Cases.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -780,121 +780,88 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>GA_009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Verify Add Members action</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>User is logged in, no users available to add</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Verify empty state when no users to add</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>1. Open Add Members dialog.
 2. Observe when all users are already members.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Empty state message should display (e.g., "No users available to add").</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>GA_010</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>User is non-admin member</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Verify Add Members not available for non-admin</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1. Login as non-admin member.
 2. Open Group Info panel.
 3. Observe Add Members option.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Add Members option should be hidden or disabled for non-admin users.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>GA_011</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Verify Delete Chat action</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and Group Info is open</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Verify Delete Chat option is visible</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1. Open Group Info panel.
-2. Observe action options.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>"Delete Chat" option with trash icon should be visible (grayed out if disabled).</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
@@ -902,153 +869,120 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>GA_012</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="n"/>
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>GA_011</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Verify Delete Chat action</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and Group Info is open</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Verify Delete Chat option is visible</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Group Info panel.
+2. Observe action options.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>"Delete Chat" option with trash icon should be visible (grayed out if disabled).</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>GA_012</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Verify Delete Chat click shows confirmation</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Click on "Delete Chat".
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Confirmation dialog should appear asking to confirm deletion.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>GA_013</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>User is logged in and confirmation shown</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Verify Delete Chat confirmation deletes messages</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1. Click Delete Chat.
 2. Confirm deletion.
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Chat messages should be deleted; group should remain with empty chat.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>GA_014</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Verify Delete Chat action</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Delete Chat is disabled</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Verify Delete Chat disabled state</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1. Open Group Info panel.
-2. Observe Delete Chat option when disabled.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Delete Chat should appear grayed out and not clickable.</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>GA_015</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Verify Leave action</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and Group Info is open</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Verify Leave option is visible</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1. Open Group Info panel.
-2. Observe action options.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>"Leave" option with exit icon should be visible in orange/red color.</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
@@ -1056,121 +990,72 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>GA_016</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="n"/>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Verify Leave click shows confirmation</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1. Open Group Info panel.
-2. Click on "Leave".
-3. Observe result.</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Confirmation dialog should appear asking to confirm leaving group.</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GA_017</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
+          <t>GA_014</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Verify Delete Chat action</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and confirmation shown</t>
+          <t>User is logged in, Delete Chat is disabled</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Verify Leave confirmation removes user from group</t>
+          <t>Verify Delete Chat disabled state</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1. Click Leave.
-2. Confirm leaving.
-3. Observe result.</t>
+          <t>1. Open Group Info panel.
+2. Observe Delete Chat option when disabled.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>User should be removed from group; group should disappear from user's list.</t>
+          <t>Delete Chat should appear grayed out and not clickable.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>GA_018</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Verify Leave action</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>User is group owner</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Verify owner cannot leave without transferring ownership</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1. Login as group owner.
-2. Open Group Info.
-3. Click Leave.</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Warning should display that owner must transfer ownership or delete group.</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GA_019</t>
+          <t>GA_015</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1180,7 +1065,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Verify Delete and Exit action</t>
+          <t>Verify Leave action</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1190,7 +1075,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Verify Delete and Exit option is visible</t>
+          <t>Verify Leave option is visible</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1201,7 +1086,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>"Delete and Exit" option with trash icon should be visible in red color.</t>
+          <t>"Leave" option with exit icon should be visible in orange/red color.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1213,7 +1098,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GA_020</t>
+          <t>GA_016</t>
         </is>
       </c>
       <c r="B21" s="2" t="n"/>
@@ -1221,19 +1106,19 @@
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Verify Delete and Exit click shows confirmation</t>
+          <t>Verify Leave click shows confirmation</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
-2. Click on "Delete and Exit".
+2. Click on "Leave".
 3. Observe result.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Confirmation dialog should appear warning about permanent deletion.</t>
+          <t>Confirmation dialog should appear asking to confirm leaving group.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1245,31 +1130,31 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GA_021</t>
+          <t>GA_017</t>
         </is>
       </c>
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>User is owner and confirmation shown</t>
+          <t>User is logged in and confirmation shown</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Verify Delete and Exit deletes group completely</t>
+          <t>Verify Leave confirmation removes user from group</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1. Click Delete and Exit.
-2. Confirm deletion.
+          <t>1. Click Leave.
+2. Confirm leaving.
 3. Observe result.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Group should be permanently deleted for all members.</t>
+          <t>User should be removed from group; group should disappear from user's list.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1279,84 +1164,51 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>GA_022</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Verify Delete and Exit action</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>User is non-owner member</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Verify Delete and Exit not available for non-owner</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1. Login as non-owner member.
-2. Open Group Info panel.
-3. Observe Delete and Exit option.</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Delete and Exit option should be hidden or disabled for non-owner users.</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GA_023</t>
+          <t>GA_018</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Verify View Members tab</t>
+          <t>Verify Leave action</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and Group Info is open</t>
+          <t>User is group owner</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Verify View Members tab is visible</t>
+          <t>Verify owner cannot leave without transferring ownership</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1. Open Group Info panel.
-2. Observe tabs section.</t>
+          <t>1. Login as group owner.
+2. Open Group Info.
+3. Click Leave.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>"View Members" tab should be visible and selected by default.</t>
+          <t>Warning should display that owner must transfer ownership or delete group.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1366,76 +1218,62 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>GA_024</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="n"/>
       <c r="B25" s="2" t="n"/>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Verify View Members tab shows member list</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1. Open Group Info panel.
-2. Click View Members tab.
-3. Observe list.</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>List of group members should display with profile pictures and names.</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GA_025</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
+          <t>GA_019</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Verify Delete and Exit action</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and View Members is active</t>
+          <t>User is logged in and Group Info is open</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Verify member profile picture display</t>
+          <t>Verify Delete and Exit option is visible</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1. View Members tab is active.
-2. Observe member avatars.</t>
+          <t>1. Open Group Info panel.
+2. Observe action options.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Each member should show profile picture or default avatar.</t>
+          <t>"Delete and Exit" option with trash icon should be visible in red color.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GA_026</t>
+          <t>GA_020</t>
         </is>
       </c>
       <c r="B27" s="2" t="n"/>
@@ -1443,123 +1281,109 @@
       <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Verify member name display</t>
+          <t>Verify Delete and Exit click shows confirmation</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1. View Members tab is active.
-2. Observe member names.</t>
+          <t>1. Open Group Info panel.
+2. Click on "Delete and Exit".
+3. Observe result.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Member names should display (e.g., "Nancy Grace", "John Paul", "George Alan").</t>
+          <t>Confirmation dialog should appear warning about permanent deletion.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GA_027</t>
+          <t>GA_021</t>
         </is>
       </c>
       <c r="B28" s="2" t="n"/>
       <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>User is owner and confirmation shown</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Verify owner badge display</t>
+          <t>Verify Delete and Exit deletes group completely</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1. View Members tab is active.
-2. Find group owner in list.</t>
+          <t>1. Click Delete and Exit.
+2. Confirm deletion.
+3. Observe result.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Owner should have "Owner" badge displayed (purple badge).</t>
+          <t>Group should be permanently deleted for all members.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>GA_028</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="n"/>
       <c r="B29" s="2" t="n"/>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Verify online status indicator</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1. View Members tab is active.
-2. Observe online indicators.</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Green dot should indicate online members.</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GA_029</t>
+          <t>GA_022</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Verify Banned Members tab</t>
+          <t>Verify Delete and Exit action</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and Group Info is open</t>
+          <t>User is non-owner member</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Verify Banned Members tab is visible</t>
+          <t>Verify Delete and Exit not available for non-owner</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1. Open Group Info panel.
-2. Observe tabs section.</t>
+          <t>1. Login as non-owner member.
+2. Open Group Info panel.
+3. Observe Delete and Exit option.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>"Banned Members" tab should be visible next to View Members.</t>
+          <t>Delete and Exit option should be hidden or disabled for non-owner users.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1569,132 +1393,98 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>GA_030</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="n"/>
       <c r="B31" s="2" t="n"/>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Verify Banned Members tab click</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>1. Open Group Info panel.
-2. Click Banned Members tab.
-3. Observe result.</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Banned Members tab should become active; list of banned users should display.</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GA_031</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
+          <t>GA_023</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Verify View Members tab</t>
+        </is>
+      </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>User is admin and Banned Members is active</t>
+          <t>User is logged in and Group Info is open</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Verify unban option for banned members</t>
+          <t>Verify View Members tab is visible</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1. Click Banned Members tab.
-2. Find banned user.
-3. Observe options.</t>
+          <t>1. Open Group Info panel.
+2. Observe tabs section.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Unban option should be available for each banned member.</t>
+          <t>"View Members" tab should be visible and selected by default.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GA_032</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Verify Banned Members tab</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, no banned members</t>
-        </is>
-      </c>
+          <t>GA_024</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Verify empty Banned Members state</t>
+          <t>Verify View Members tab shows member list</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1. Click Banned Members tab.
-2. Observe when no users are banned.</t>
+          <t>1. Open Group Info panel.
+2. Click View Members tab.
+3. Observe list.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Empty state message should display (e.g., "No banned members").</t>
+          <t>List of group members should display with profile pictures and names.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GA_033</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Verify Search in members</t>
-        </is>
-      </c>
+          <t>GA_025</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="inlineStr">
         <is>
           <t>User is logged in and View Members is active</t>
@@ -1702,31 +1492,30 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Verify search field is visible</t>
+          <t>Verify member profile picture display</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1. Open Group Info panel.
-2. View Members tab is active.
-3. Observe search field.</t>
+          <t>1. View Members tab is active.
+2. Observe member avatars.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Search field should be visible with placeholder "Search".</t>
+          <t>Each member should show profile picture or default avatar.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GA_034</t>
+          <t>GA_026</t>
         </is>
       </c>
       <c r="B35" s="2" t="n"/>
@@ -1734,31 +1523,30 @@
       <c r="D35" s="2" t="n"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Verify search by member name</t>
+          <t>Verify member name display</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
           <t>1. View Members tab is active.
-2. Type "Nancy" in search field.
-3. Observe results.</t>
+2. Observe member names.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>"Nancy Grace" should appear in filtered results.</t>
+          <t>Member names should display (e.g., "Nancy Grace", "John Paul", "George Alan").</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GA_035</t>
+          <t>GA_027</t>
         </is>
       </c>
       <c r="B36" s="2" t="n"/>
@@ -1766,74 +1554,61 @@
       <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Verify search clears correctly</t>
+          <t>Verify owner badge display</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1. Type search query.
-2. Clear search field.
-3. Observe results.</t>
+          <t>1. View Members tab is active.
+2. Find group owner in list.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Full member list should be restored.</t>
+          <t>Owner should have "Owner" badge displayed (purple badge).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GA_036</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Verify Search in members</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and View Members is active</t>
-        </is>
-      </c>
+          <t>GA_028</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Verify search with no results</t>
+          <t>Verify online status indicator</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1. Type "XYZ123" in search field.
-2. Observe results.</t>
+          <t>1. View Members tab is active.
+2. Observe online indicators.</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Empty state should display (e.g., "No members found").</t>
+          <t>Green dot should indicate online members.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GA_037</t>
+          <t>GA_029</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1843,29 +1618,28 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Verify Kick action</t>
+          <t>Verify Banned Members tab</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>User is admin and View Members is active</t>
+          <t>User is logged in and Group Info is open</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Verify Kick option in member dropdown</t>
+          <t>Verify Banned Members tab is visible</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1. View Members tab is active.
-2. Click dropdown on a member.
-3. Observe options.</t>
+          <t>1. Open Group Info panel.
+2. Observe tabs section.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>"Kick" option should be visible in dropdown menu.</t>
+          <t>"Banned Members" tab should be visible next to View Members.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1877,7 +1651,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GA_038</t>
+          <t>GA_030</t>
         </is>
       </c>
       <c r="B39" s="2" t="n"/>
@@ -1885,19 +1659,19 @@
       <c r="D39" s="2" t="n"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Verify Kick click shows confirmation</t>
+          <t>Verify Banned Members tab click</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1. Click dropdown on a member.
-2. Click "Kick".
+          <t>1. Open Group Info panel.
+2. Click Banned Members tab.
 3. Observe result.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Confirmation dialog should appear asking to confirm kick.</t>
+          <t>Banned Members tab should become active; list of banned users should display.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1909,415 +1683,309 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GA_039</t>
+          <t>GA_031</t>
         </is>
       </c>
       <c r="B40" s="2" t="n"/>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>User is admin and confirmation shown</t>
+          <t>User is admin and Banned Members is active</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Verify Kick removes member from group</t>
+          <t>Verify unban option for banned members</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1. Click Kick.
-2. Confirm action.
-3. Observe result.</t>
+          <t>1. Click Banned Members tab.
+2. Find banned user.
+3. Observe options.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Member should be removed from group; member count should decrease.</t>
+          <t>Unban option should be available for each banned member.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>GA_040</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Verify Kick action</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>User is non-admin member</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Verify Kick not available for non-admin</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>1. Login as non-admin.
-2. View Members tab.
-3. Observe member options.</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Kick option should not be visible for non-admin users.</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GA_041</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n"/>
-      <c r="C42" s="2" t="n"/>
+          <t>GA_032</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Verify Banned Members tab</t>
+        </is>
+      </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>User is admin viewing owner</t>
+          <t>User is logged in, no banned members</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Verify cannot kick group owner</t>
+          <t>Verify empty Banned Members state</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1. Login as admin.
-2. View Members tab.
-3. Click dropdown on owner.</t>
+          <t>1. Click Banned Members tab.
+2. Observe when no users are banned.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Kick option should not be available for group owner.</t>
+          <t>Empty state message should display (e.g., "No banned members").</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>GA_042</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>GA_033</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Verify Ban action</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Verify Search in members</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and View Members is active</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Verify search field is visible</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Group Info panel.
+2. View Members tab is active.
+3. Observe search field.</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Search field should be visible with placeholder "Search".</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>GA_034</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Verify search by member name</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>1. View Members tab is active.
+2. Type "Nancy" in search field.
+3. Observe results.</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>"Nancy Grace" should appear in filtered results.</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>GA_035</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Verify search clears correctly</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>1. Type search query.
+2. Clear search field.
+3. Observe results.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Full member list should be restored.</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="2" t="n"/>
+      <c r="H47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>GA_036</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Verify Search in members</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and View Members is active</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Verify search with no results</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>1. Type "XYZ123" in search field.
+2. Observe results.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Empty state should display (e.g., "No members found").</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>GA_037</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Verify Kick action</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>User is admin and View Members is active</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Verify Ban option in member dropdown</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Verify Kick option in member dropdown</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. View Members tab is active.
 2. Click dropdown on a member.
 3. Observe options.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>"Ban" option should be visible in dropdown menu.</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>GA_043</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Verify Ban click shows confirmation</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>1. Click dropdown on a member.
-2. Click "Ban".
-3. Observe result.</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Confirmation dialog should appear asking to confirm ban.</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>GA_044</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n"/>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>User is admin and confirmation shown</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Verify Ban removes and blocks member</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1. Click Ban.
-2. Confirm action.
-3. Observe result.</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Member should be removed and added to Banned Members list.</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>GA_045</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Verify Ban action</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>User is non-admin member</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Verify Ban not available for non-admin</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>1. Login as non-admin.
-2. View Members tab.
-3. Observe member options.</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Ban option should not be visible for non-admin users.</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>GA_046</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n"/>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>User is admin viewing owner</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Verify cannot ban group owner</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>1. Login as admin.
-2. View Members tab.
-3. Click dropdown on owner.</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Ban option should not be available for group owner.</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>GA_047</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Verify Change Scope action</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>User is admin and View Members is active</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Verify Change Scope option in member dropdown</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>1. View Members tab is active.
-2. Click dropdown on a member.
-3. Observe options.</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>"Change Scope" option should be visible in dropdown menu.</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>GA_048</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="n"/>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n"/>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Verify Change Scope click opens options</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>1. Click dropdown on a member.
-2. Click "Change Scope".
-3. Observe result.</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Scope options should appear (e.g., Admin, Moderator, Member).</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>GA_049</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="n"/>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>User is admin and scope options shown</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Verify promoting member to admin</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>1. Click Change Scope.
-2. Select "Admin".
-3. Confirm action.</t>
-        </is>
-      </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Member's role should change to Admin.</t>
+          <t>"Kick" option should be visible in dropdown menu.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2329,7 +1997,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GA_050</t>
+          <t>GA_038</t>
         </is>
       </c>
       <c r="B51" s="2" t="n"/>
@@ -2337,178 +2005,690 @@
       <c r="D51" s="2" t="n"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
+          <t>Verify Kick click shows confirmation</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>1. Click dropdown on a member.
+2. Click "Kick".
+3. Observe result.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Confirmation dialog should appear asking to confirm kick.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>GA_039</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>User is admin and confirmation shown</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Verify Kick removes member from group</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>1. Click Kick.
+2. Confirm action.
+3. Observe result.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Member should be removed from group; member count should decrease.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="n"/>
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>GA_040</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Verify Kick action</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>User is non-admin member</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Verify Kick not available for non-admin</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as non-admin.
+2. View Members tab.
+3. Observe member options.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Kick option should not be visible for non-admin users.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>GA_041</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>User is admin viewing owner</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Verify cannot kick group owner</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as admin.
+2. View Members tab.
+3. Click dropdown on owner.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Kick option should not be available for group owner.</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="n"/>
+      <c r="H56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>GA_042</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Verify Ban action</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>User is admin and View Members is active</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Verify Ban option in member dropdown</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>1. View Members tab is active.
+2. Click dropdown on a member.
+3. Observe options.</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>"Ban" option should be visible in dropdown menu.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>GA_043</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Verify Ban click shows confirmation</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>1. Click dropdown on a member.
+2. Click "Ban".
+3. Observe result.</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Confirmation dialog should appear asking to confirm ban.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>GA_044</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>User is admin and confirmation shown</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Verify Ban removes and blocks member</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>1. Click Ban.
+2. Confirm action.
+3. Observe result.</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Member should be removed and added to Banned Members list.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n"/>
+      <c r="E60" s="2" t="n"/>
+      <c r="F60" s="2" t="n"/>
+      <c r="G60" s="2" t="n"/>
+      <c r="H60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>GA_045</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Verify Ban action</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>User is non-admin member</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Verify Ban not available for non-admin</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as non-admin.
+2. View Members tab.
+3. Observe member options.</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Ban option should not be visible for non-admin users.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>GA_046</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>User is admin viewing owner</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Verify cannot ban group owner</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as admin.
+2. View Members tab.
+3. Click dropdown on owner.</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Ban option should not be available for group owner.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n"/>
+      <c r="B63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n"/>
+      <c r="E63" s="2" t="n"/>
+      <c r="F63" s="2" t="n"/>
+      <c r="G63" s="2" t="n"/>
+      <c r="H63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>GA_047</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Verify Change Scope action</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>User is admin and View Members is active</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Verify Change Scope option in member dropdown</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>1. View Members tab is active.
+2. Click dropdown on a member.
+3. Observe options.</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>"Change Scope" option should be visible in dropdown menu.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>GA_048</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Verify Change Scope click opens options</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>1. Click dropdown on a member.
+2. Click "Change Scope".
+3. Observe result.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Scope options should appear (e.g., Admin, Moderator, Member).</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>GA_049</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>User is admin and scope options shown</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Verify promoting member to admin</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>1. Click Change Scope.
+2. Select "Admin".
+3. Confirm action.</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Member's role should change to Admin.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>GA_050</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>Verify demoting admin to member</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Click Change Scope on admin.
 2. Select "Member".
 3. Confirm action.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>Admin's role should change to Member.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="n"/>
+      <c r="F68" s="2" t="n"/>
+      <c r="G68" s="2" t="n"/>
+      <c r="H68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>GA_051</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Verify Change Scope action</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>User is non-admin member</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Verify Change Scope not available for non-admin</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Login as non-admin.
 2. View Members tab.
 3. Observe member options.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>Change Scope option should not be visible for non-admin users.</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>GA_052</t>
         </is>
       </c>
-      <c r="B53" s="2" t="n"/>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>User is admin viewing owner</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Verify cannot change owner's scope</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Login as admin.
 2. View Members tab.
 3. Click dropdown on owner.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>Change Scope option should not be available for group owner.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n"/>
+      <c r="B71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n"/>
+      <c r="E71" s="2" t="n"/>
+      <c r="F71" s="2" t="n"/>
+      <c r="G71" s="2" t="n"/>
+      <c r="H71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>GA_053</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Verify UI responsiveness</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Verify Group Info panel on desktop</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Open application on desktop.
 2. Open Group Info panel.
 3. Resize browser.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>Panel should adjust dynamically; all elements should remain functional.</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>GA_054</t>
         </is>
       </c>
-      <c r="B55" s="2" t="n"/>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n"/>
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Verify Group Info panel on mobile</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Open application on mobile.
 2. Open Group Info panel.
 3. Check layout.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>Panel should fit screen properly; scrolling should work for long lists.</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
@@ -3181,7 +3361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3373,38 +3553,48 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>GA_072</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Edge Case: Group Actions</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Verify simultaneous admin actions on same member</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1. Two admins try to kick the same member at the same time.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>One action should succeed, the other should fail gracefully. No data corruption.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>

--- a/Group_Actions/Group_Actions_Test_Cases.xlsx
+++ b/Group_Actions/Group_Actions_Test_Cases.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -780,207 +780,262 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n"/>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>GA_011</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Verify Delete Chat action</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and Group Info is open</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Verify Delete Chat option is visible</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Group Info panel.
+2. Observe action options.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>"Delete Chat" option with trash icon should be visible (grayed out if disabled).</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GA_009</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Verify Add Members action</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, no users available to add</t>
-        </is>
-      </c>
+          <t>GA_012</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Verify empty state when no users to add</t>
+          <t>Verify Delete Chat click shows confirmation</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1. Open Add Members dialog.
-2. Observe when all users are already members.</t>
+          <t>1. Open Group Info panel.
+2. Click on "Delete Chat".
+3. Observe result.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Empty state message should display (e.g., "No users available to add").</t>
+          <t>Confirmation dialog should appear asking to confirm deletion.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GA_010</t>
+          <t>GA_013</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>User is non-admin member</t>
+          <t>User is logged in and confirmation shown</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Verify Add Members not available for non-admin</t>
+          <t>Verify Delete Chat confirmation deletes messages</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1. Login as non-admin member.
-2. Open Group Info panel.
-3. Observe Add Members option.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Add Members option should be hidden or disabled for non-admin users.</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n"/>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>GA_011</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Verify Delete Chat action</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and Group Info is open</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Verify Delete Chat option is visible</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1. Open Group Info panel.
-2. Observe action options.</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>"Delete Chat" option with trash icon should be visible (grayed out if disabled).</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>GA_012</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Verify Delete Chat click shows confirmation</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1. Open Group Info panel.
-2. Click on "Delete Chat".
-3. Observe result.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Confirmation dialog should appear asking to confirm deletion.</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>GA_013</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and confirmation shown</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Verify Delete Chat confirmation deletes messages</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1. Click Delete Chat.
 2. Confirm deletion.
 3. Observe result.</t>
         </is>
       </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Chat messages should be deleted; group should remain with empty chat.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>GA_015</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Verify Leave action</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and Group Info is open</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Verify Leave option is visible</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Group Info panel.
+2. Observe action options.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>"Leave" option with exit icon should be visible in orange/red color.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>GA_016</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Verify Leave click shows confirmation</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Group Info panel.
+2. Click on "Leave".
+3. Observe result.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Confirmation dialog should appear asking to confirm leaving group.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>GA_017</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and confirmation shown</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Verify Leave confirmation removes user from group</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1. Click Leave.
+2. Confirm leaving.
+3. Observe result.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>User should be removed from group; group should disappear from user's list.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>GA_019</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Verify Delete and Exit action</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and Group Info is open</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Verify Delete and Exit option is visible</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Group Info panel.
+2. Observe action options.</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Chat messages should be deleted; group should remain with empty chat.</t>
+          <t>"Delete and Exit" option with trash icon should be visible in red color.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -990,103 +1045,140 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>GA_020</t>
+        </is>
+      </c>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="n"/>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Verify Delete and Exit click shows confirmation</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Group Info panel.
+2. Click on "Delete and Exit".
+3. Observe result.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Confirmation dialog should appear warning about permanent deletion.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GA_014</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Verify Delete Chat action</t>
-        </is>
-      </c>
+          <t>GA_021</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, Delete Chat is disabled</t>
+          <t>User is owner and confirmation shown</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Verify Delete Chat disabled state</t>
+          <t>Verify Delete and Exit deletes group completely</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>1. Click Delete and Exit.
+2. Confirm deletion.
+3. Observe result.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Group should be permanently deleted for all members.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>GA_023</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Verify View Members tab</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and Group Info is open</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Verify View Members tab is visible</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>1. Open Group Info panel.
-2. Observe Delete Chat option when disabled.</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Delete Chat should appear grayed out and not clickable.</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
+2. Observe tabs section.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>"View Members" tab should be visible and selected by default.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GA_015</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Verify Leave action</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and Group Info is open</t>
-        </is>
-      </c>
+          <t>GA_024</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Verify Leave option is visible</t>
+          <t>Verify View Members tab shows member list</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
-2. Observe action options.</t>
+2. Click View Members tab.
+3. Observe list.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>"Leave" option with exit icon should be visible in orange/red color.</t>
+          <t>List of group members should display with profile pictures and names.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1098,170 +1190,198 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GA_016</t>
+          <t>GA_025</t>
         </is>
       </c>
       <c r="B21" s="2" t="n"/>
       <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and View Members is active</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Verify Leave click shows confirmation</t>
+          <t>Verify member profile picture display</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1. Open Group Info panel.
-2. Click on "Leave".
-3. Observe result.</t>
+          <t>1. View Members tab is active.
+2. Observe member avatars.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Confirmation dialog should appear asking to confirm leaving group.</t>
+          <t>Each member should show profile picture or default avatar.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>GA_017</t>
+          <t>GA_026</t>
         </is>
       </c>
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and confirmation shown</t>
-        </is>
-      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Verify Leave confirmation removes user from group</t>
+          <t>Verify member name display</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1. Click Leave.
-2. Confirm leaving.
-3. Observe result.</t>
+          <t>1. View Members tab is active.
+2. Observe member names.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>User should be removed from group; group should disappear from user's list.</t>
+          <t>Member names should display (e.g., "Nancy Grace", "John Paul", "George Alan").</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>GA_027</t>
+        </is>
+      </c>
       <c r="B23" s="2" t="n"/>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Verify owner badge display</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1. View Members tab is active.
+2. Find group owner in list.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Owner should have "Owner" badge displayed (purple badge).</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>GA_018</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Verify Leave action</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>User is group owner</t>
-        </is>
-      </c>
+          <t>GA_028</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Verify owner cannot leave without transferring ownership</t>
+          <t>Verify online status indicator</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1. Login as group owner.
-2. Open Group Info.
-3. Click Leave.</t>
+          <t>1. View Members tab is active.
+2. Observe online indicators.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Warning should display that owner must transfer ownership or delete group.</t>
+          <t>Green dot should indicate online members.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n"/>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>GA_029</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Verify Banned Members tab</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and Group Info is open</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Verify Banned Members tab is visible</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Group Info panel.
+2. Observe tabs section.</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>"Banned Members" tab should be visible next to View Members.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GA_019</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Verify Delete and Exit action</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and Group Info is open</t>
-        </is>
-      </c>
+          <t>GA_030</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Verify Delete and Exit option is visible</t>
+          <t>Verify Banned Members tab click</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
-2. Observe action options.</t>
+2. Click Banned Members tab.
+3. Observe result.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>"Delete and Exit" option with trash icon should be visible in red color.</t>
+          <t>Banned Members tab should become active; list of banned users should display.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1273,63 +1393,75 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GA_020</t>
+          <t>GA_031</t>
         </is>
       </c>
       <c r="B27" s="2" t="n"/>
       <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>User is admin and Banned Members is active</t>
+        </is>
+      </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Verify Delete and Exit click shows confirmation</t>
+          <t>Verify unban option for banned members</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1. Open Group Info panel.
-2. Click on "Delete and Exit".
-3. Observe result.</t>
+          <t>1. Click Banned Members tab.
+2. Find banned user.
+3. Observe options.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Confirmation dialog should appear warning about permanent deletion.</t>
+          <t>Unban option should be available for each banned member.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GA_021</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
+          <t>GA_033</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Verify Search in members</t>
+        </is>
+      </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>User is owner and confirmation shown</t>
+          <t>User is logged in and View Members is active</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Verify Delete and Exit deletes group completely</t>
+          <t>Verify search field is visible</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1. Click Delete and Exit.
-2. Confirm deletion.
-3. Observe result.</t>
+          <t>1. Open Group Info panel.
+2. View Members tab is active.
+3. Observe search field.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Group should be permanently deleted for all members.</t>
+          <t>Search field should be visible with placeholder "Search".</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1339,104 +1471,137 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>GA_034</t>
+        </is>
+      </c>
       <c r="B29" s="2" t="n"/>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Verify search by member name</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1. View Members tab is active.
+2. Type "Nancy" in search field.
+3. Observe results.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>"Nancy Grace" should appear in filtered results.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>GA_022</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Verify Delete and Exit action</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>User is non-owner member</t>
-        </is>
-      </c>
+          <t>GA_035</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Verify Delete and Exit not available for non-owner</t>
+          <t>Verify search clears correctly</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1. Login as non-owner member.
-2. Open Group Info panel.
-3. Observe Delete and Exit option.</t>
+          <t>1. Type search query.
+2. Clear search field.
+3. Observe results.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Delete and Exit option should be hidden or disabled for non-owner users.</t>
+          <t>Full member list should be restored.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>GA_037</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Verify Kick action</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>User is admin and View Members is active</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Verify Kick option in member dropdown</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>1. View Members tab is active.
+2. Click dropdown on a member.
+3. Observe options.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>"Kick" option should be visible in dropdown menu.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GA_023</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Verify View Members tab</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and Group Info is open</t>
-        </is>
-      </c>
+          <t>GA_038</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Verify View Members tab is visible</t>
+          <t>Verify Kick click shows confirmation</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1. Open Group Info panel.
-2. Observe tabs section.</t>
+          <t>1. Click dropdown on a member.
+2. Click "Kick".
+3. Observe result.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>"View Members" tab should be visible and selected by default.</t>
+          <t>Confirmation dialog should appear asking to confirm kick.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -1448,27 +1613,31 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GA_024</t>
+          <t>GA_039</t>
         </is>
       </c>
       <c r="B33" s="2" t="n"/>
       <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>User is admin and confirmation shown</t>
+        </is>
+      </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Verify View Members tab shows member list</t>
+          <t>Verify Kick removes member from group</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1. Open Group Info panel.
-2. Click View Members tab.
-3. Observe list.</t>
+          <t>1. Click Kick.
+2. Confirm action.
+3. Observe result.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>List of group members should display with profile pictures and names.</t>
+          <t>Member should be removed from group; member count should decrease.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1480,42 +1649,51 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GA_025</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
+          <t>GA_042</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Verify Ban action</t>
+        </is>
+      </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and View Members is active</t>
+          <t>User is admin and View Members is active</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Verify member profile picture display</t>
+          <t>Verify Ban option in member dropdown</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. View Members tab is active.
-2. Observe member avatars.</t>
+2. Click dropdown on a member.
+3. Observe options.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Each member should show profile picture or default avatar.</t>
+          <t>"Ban" option should be visible in dropdown menu.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GA_026</t>
+          <t>GA_043</t>
         </is>
       </c>
       <c r="B35" s="2" t="n"/>
@@ -1523,123 +1701,131 @@
       <c r="D35" s="2" t="n"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Verify member name display</t>
+          <t>Verify Ban click shows confirmation</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1. View Members tab is active.
-2. Observe member names.</t>
+          <t>1. Click dropdown on a member.
+2. Click "Ban".
+3. Observe result.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Member names should display (e.g., "Nancy Grace", "John Paul", "George Alan").</t>
+          <t>Confirmation dialog should appear asking to confirm ban.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GA_027</t>
+          <t>GA_044</t>
         </is>
       </c>
       <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>User is admin and confirmation shown</t>
+        </is>
+      </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Verify owner badge display</t>
+          <t>Verify Ban removes and blocks member</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1. View Members tab is active.
-2. Find group owner in list.</t>
+          <t>1. Click Ban.
+2. Confirm action.
+3. Observe result.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Owner should have "Owner" badge displayed (purple badge).</t>
+          <t>Member should be removed and added to Banned Members list.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GA_028</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
+          <t>GA_047</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Verify Change Scope action</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>User is admin and View Members is active</t>
+        </is>
+      </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Verify online status indicator</t>
+          <t>Verify Change Scope option in member dropdown</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1. View Members tab is active.
-2. Observe online indicators.</t>
+2. Click dropdown on a member.
+3. Observe options.</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Green dot should indicate online members.</t>
+          <t>"Change Scope" option should be visible in dropdown menu.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Low / Low</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GA_029</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Verify Banned Members tab</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and Group Info is open</t>
-        </is>
-      </c>
+          <t>GA_048</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Verify Banned Members tab is visible</t>
+          <t>Verify Change Scope click opens options</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1. Open Group Info panel.
-2. Observe tabs section.</t>
+          <t>1. Click dropdown on a member.
+2. Click "Change Scope".
+3. Observe result.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>"Banned Members" tab should be visible next to View Members.</t>
+          <t>Scope options should appear (e.g., Admin, Moderator, Member).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1651,27 +1837,31 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GA_030</t>
+          <t>GA_049</t>
         </is>
       </c>
       <c r="B39" s="2" t="n"/>
       <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>User is admin and scope options shown</t>
+        </is>
+      </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Verify Banned Members tab click</t>
+          <t>Verify promoting member to admin</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1. Open Group Info panel.
-2. Click Banned Members tab.
-3. Observe result.</t>
+          <t>1. Click Change Scope.
+2. Select "Admin".
+3. Confirm action.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Banned Members tab should become active; list of banned users should display.</t>
+          <t>Member's role should change to Admin.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -1683,89 +1873,108 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GA_031</t>
+          <t>GA_050</t>
         </is>
       </c>
       <c r="B40" s="2" t="n"/>
       <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>User is admin and Banned Members is active</t>
-        </is>
-      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Verify unban option for banned members</t>
+          <t>Verify demoting admin to member</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1. Click Banned Members tab.
-2. Find banned user.
-3. Observe options.</t>
+          <t>1. Click Change Scope on admin.
+2. Select "Member".
+3. Confirm action.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Unban option should be available for each banned member.</t>
+          <t>Admin's role should change to Member.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>GA_053</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Verify UI responsiveness</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Verify Group Info panel on desktop</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>1. Open application on desktop.
+2. Open Group Info panel.
+3. Resize browser.</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Panel should adjust dynamically; all elements should remain functional.</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
           <t>High / Medium</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n"/>
-      <c r="B41" s="2" t="n"/>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n"/>
-      <c r="G41" s="2" t="n"/>
-      <c r="H41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GA_032</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Verify Banned Members tab</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, no banned members</t>
-        </is>
-      </c>
+          <t>GA_054</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Verify empty Banned Members state</t>
+          <t>Verify Group Info panel on mobile</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1. Click Banned Members tab.
-2. Observe when no users are banned.</t>
+          <t>1. Open application on mobile.
+2. Open Group Info panel.
+3. Check layout.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Empty state message should display (e.g., "No banned members").</t>
+          <t>Panel should fit screen properly; scrolling should work for long lists.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
@@ -1782,71 +1991,74 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GA_033</t>
+          <t>GA_009</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Verify Search in members</t>
+          <t>Verify Add Members action</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and View Members is active</t>
+          <t>User is logged in, no users available to add</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Verify search field is visible</t>
+          <t>Verify empty state when no users to add</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1. Open Group Info panel.
-2. View Members tab is active.
-3. Observe search field.</t>
+          <t>1. Open Add Members dialog.
+2. Observe when all users are already members.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Search field should be visible with placeholder "Search".</t>
+          <t>Empty state message should display (e.g., "No users available to add").</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GA_034</t>
+          <t>GA_010</t>
         </is>
       </c>
       <c r="B45" s="2" t="n"/>
       <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n"/>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>User is non-admin member</t>
+        </is>
+      </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Verify search by member name</t>
+          <t>Verify Add Members not available for non-admin</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1. View Members tab is active.
-2. Type "Nancy" in search field.
-3. Observe results.</t>
+          <t>1. Login as non-admin member.
+2. Open Group Info panel.
+3. Observe Add Members option.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>"Nancy Grace" should appear in filtered results.</t>
+          <t>Add Members option should be hidden or disabled for non-admin users.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -1858,27 +2070,38 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GA_035</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n"/>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
+          <t>GA_014</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Verify Delete Chat action</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Delete Chat is disabled</t>
+        </is>
+      </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Verify search clears correctly</t>
+          <t>Verify Delete Chat disabled state</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1. Type search query.
-2. Clear search field.
-3. Observe results.</t>
+          <t>1. Open Group Info panel.
+2. Observe Delete Chat option when disabled.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Full member list should be restored.</t>
+          <t>Delete Chat should appear grayed out and not clickable.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -1888,136 +2111,215 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n"/>
-      <c r="B47" s="2" t="n"/>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="n"/>
-      <c r="F47" s="2" t="n"/>
-      <c r="G47" s="2" t="n"/>
-      <c r="H47" s="2" t="n"/>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>GA_018</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Verify Leave action</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>User is group owner</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Verify owner cannot leave without transferring ownership</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as group owner.
+2. Open Group Info.
+3. Click Leave.</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Warning should display that owner must transfer ownership or delete group.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>GA_022</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Verify Delete and Exit action</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>User is non-owner member</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Verify Delete and Exit not available for non-owner</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>1. Login as non-owner member.
+2. Open Group Info panel.
+3. Observe Delete and Exit option.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Delete and Exit option should be hidden or disabled for non-owner users.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>GA_032</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Verify Banned Members tab</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, no banned members</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Verify empty Banned Members state</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>1. Click Banned Members tab.
+2. Observe when no users are banned.</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Empty state message should display (e.g., "No banned members").</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>GA_036</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Verify Search in members</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>User is logged in and View Members is active</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Verify search with no results</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Type "XYZ123" in search field.
 2. Observe results.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>Empty state should display (e.g., "No members found").</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n"/>
-      <c r="B49" s="2" t="n"/>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n"/>
-      <c r="E49" s="2" t="n"/>
-      <c r="F49" s="2" t="n"/>
-      <c r="G49" s="2" t="n"/>
-      <c r="H49" s="2" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>GA_037</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Verify Kick action</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>User is admin and View Members is active</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Verify Kick option in member dropdown</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>1. View Members tab is active.
-2. Click dropdown on a member.
-3. Observe options.</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>"Kick" option should be visible in dropdown menu.</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GA_038</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="n"/>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n"/>
+          <t>GA_040</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Verify Kick action</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>User is non-admin member</t>
+        </is>
+      </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Verify Kick click shows confirmation</t>
+          <t>Verify Kick not available for non-admin</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>1. Click dropdown on a member.
-2. Click "Kick".
-3. Observe result.</t>
+          <t>1. Login as non-admin.
+2. View Members tab.
+3. Observe member options.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Confirmation dialog should appear asking to confirm kick.</t>
+          <t>Kick option should not be visible for non-admin users.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2029,31 +2331,31 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GA_039</t>
+          <t>GA_041</t>
         </is>
       </c>
       <c r="B52" s="2" t="n"/>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>User is admin and confirmation shown</t>
+          <t>User is admin viewing owner</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Verify Kick removes member from group</t>
+          <t>Verify cannot kick group owner</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1. Click Kick.
-2. Confirm action.
-3. Observe result.</t>
+          <t>1. Login as admin.
+2. View Members tab.
+3. Click dropdown on owner.</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Member should be removed from group; member count should decrease.</t>
+          <t>Kick option should not be available for group owner.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2063,634 +2365,162 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n"/>
-      <c r="B53" s="2" t="n"/>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="2" t="n"/>
-      <c r="F53" s="2" t="n"/>
-      <c r="G53" s="2" t="n"/>
-      <c r="H53" s="2" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>GA_040</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>GA_045</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Verify Kick action</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Verify Ban action</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>User is non-admin member</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Verify Kick not available for non-admin</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Verify Ban not available for non-admin</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Login as non-admin.
 2. View Members tab.
 3. Observe member options.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Kick option should not be visible for non-admin users.</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>GA_041</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n"/>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Ban option should not be visible for non-admin users.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>GA_046</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>User is admin viewing owner</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Verify cannot kick group owner</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Verify cannot ban group owner</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Login as admin.
 2. View Members tab.
 3. Click dropdown on owner.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Kick option should not be available for group owner.</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n"/>
-      <c r="B56" s="2" t="n"/>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="2" t="n"/>
-      <c r="G56" s="2" t="n"/>
-      <c r="H56" s="2" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>GA_042</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Verify Ban action</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>User is admin and View Members is active</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Verify Ban option in member dropdown</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>1. View Members tab is active.
-2. Click dropdown on a member.
-3. Observe options.</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>"Ban" option should be visible in dropdown menu.</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>GA_043</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="n"/>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n"/>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>Verify Ban click shows confirmation</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>1. Click dropdown on a member.
-2. Click "Ban".
-3. Observe result.</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Confirmation dialog should appear asking to confirm ban.</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>GA_044</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="n"/>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>User is admin and confirmation shown</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>Verify Ban removes and blocks member</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>1. Click Ban.
-2. Confirm action.
-3. Observe result.</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>Member should be removed and added to Banned Members list.</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="n"/>
-      <c r="B60" s="2" t="n"/>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="n"/>
-      <c r="F60" s="2" t="n"/>
-      <c r="G60" s="2" t="n"/>
-      <c r="H60" s="2" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>GA_045</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Ban option should not be available for group owner.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>GA_051</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Verify Ban action</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Verify Change Scope action</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>User is non-admin member</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>Verify Ban not available for non-admin</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Verify Change Scope not available for non-admin</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Login as non-admin.
 2. View Members tab.
 3. Observe member options.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Ban option should not be visible for non-admin users.</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>GA_046</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="n"/>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Change Scope option should not be visible for non-admin users.</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>GA_052</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>User is admin viewing owner</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>Verify cannot ban group owner</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Verify cannot change owner's scope</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>1. Login as admin.
 2. View Members tab.
 3. Click dropdown on owner.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>Ban option should not be available for group owner.</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="n"/>
-      <c r="B63" s="2" t="n"/>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n"/>
-      <c r="E63" s="2" t="n"/>
-      <c r="F63" s="2" t="n"/>
-      <c r="G63" s="2" t="n"/>
-      <c r="H63" s="2" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>GA_047</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Verify Change Scope action</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>User is admin and View Members is active</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Verify Change Scope option in member dropdown</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>1. View Members tab is active.
-2. Click dropdown on a member.
-3. Observe options.</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>"Change Scope" option should be visible in dropdown menu.</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>GA_048</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="n"/>
-      <c r="C65" s="2" t="n"/>
-      <c r="D65" s="2" t="n"/>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>Verify Change Scope click opens options</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>1. Click dropdown on a member.
-2. Click "Change Scope".
-3. Observe result.</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>Scope options should appear (e.g., Admin, Moderator, Member).</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>GA_049</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="n"/>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>User is admin and scope options shown</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>Verify promoting member to admin</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>1. Click Change Scope.
-2. Select "Admin".
-3. Confirm action.</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>Member's role should change to Admin.</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>GA_050</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="n"/>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n"/>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Verify demoting admin to member</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>1. Click Change Scope on admin.
-2. Select "Member".
-3. Confirm action.</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Admin's role should change to Member.</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="n"/>
-      <c r="B68" s="2" t="n"/>
-      <c r="C68" s="2" t="n"/>
-      <c r="D68" s="2" t="n"/>
-      <c r="E68" s="2" t="n"/>
-      <c r="F68" s="2" t="n"/>
-      <c r="G68" s="2" t="n"/>
-      <c r="H68" s="2" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>GA_051</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Verify Change Scope action</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>User is non-admin member</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>Verify Change Scope not available for non-admin</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>1. Login as non-admin.
-2. View Members tab.
-3. Observe member options.</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Change Scope option should not be visible for non-admin users.</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>GA_052</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="n"/>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>User is admin viewing owner</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>Verify cannot change owner's scope</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>1. Login as admin.
-2. View Members tab.
-3. Click dropdown on owner.</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Change Scope option should not be available for group owner.</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="n"/>
-      <c r="B71" s="2" t="n"/>
-      <c r="C71" s="2" t="n"/>
-      <c r="D71" s="2" t="n"/>
-      <c r="E71" s="2" t="n"/>
-      <c r="F71" s="2" t="n"/>
-      <c r="G71" s="2" t="n"/>
-      <c r="H71" s="2" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>GA_053</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Verify UI responsiveness</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>Verify Group Info panel on desktop</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>1. Open application on desktop.
-2. Open Group Info panel.
-3. Resize browser.</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Panel should adjust dynamically; all elements should remain functional.</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>GA_054</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="n"/>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n"/>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>Verify Group Info panel on mobile</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>1. Open application on mobile.
-2. Open Group Info panel.
-3. Check layout.</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Panel should fit screen properly; scrolling should work for long lists.</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
         </is>
       </c>
     </row>

--- a/Group_Actions/Group_Actions_Test_Cases.xlsx
+++ b/Group_Actions/Group_Actions_Test_Cases.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,8 +36,18 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +58,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,13 +85,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,88 +465,88 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>GA_001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Verify Group Info panel</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and group is selected</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify Group Info panel opens</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Select a group.
@@ -532,1995 +554,2629 @@
 4. Observe panel.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Group Info panel should open with group avatar, name, and member count.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>GA_002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify group avatar display in info panel</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Observe group avatar at top.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Group avatar with initials (e.g., "RA") should display in purple circle.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GA_003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify group name display in info panel</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Observe group name.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Group name (e.g., "RBAC AND SBAC") should display below avatar.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GA_004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify member count in info panel</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Observe member count.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Member count (e.g., "4 Members") should display below group name.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>GA_005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Verify close button (X) functionality</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Click X button in top right.
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Group Info panel should close.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>GA_006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Verify Add Members action</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>User is logged in and Group Info is open</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Verify Add Members option is visible</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Observe action options.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>"Add Members" option with person+ icon should be visible.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>GA_007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Verify Add Members click opens dialog</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Click on "Add Members".
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Add Members dialog/screen should open with user selection list.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>GA_008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>User is logged in and Add Members dialog is open</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Verify adding a new member to group</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. Open Add Members dialog.
 2. Select a user.
 3. Confirm addition.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Selected user should be added to group; member count should increase.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>GA_011</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Verify Delete Chat action</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>User is logged in and Group Info is open</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Verify Delete Chat option is visible</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Observe action options.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>"Delete Chat" option with trash icon should be visible (grayed out if disabled).</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>GA_012</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Verify Delete Chat click shows confirmation</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Click on "Delete Chat".
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Confirmation dialog should appear asking to confirm deletion.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>GA_013</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>User is logged in and confirmation shown</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Verify Delete Chat confirmation deletes messages</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. Click Delete Chat.
 2. Confirm deletion.
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Chat messages should be deleted; group should remain with empty chat.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>GA_015</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Verify Leave action</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>User is logged in and Group Info is open</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Verify Leave option is visible</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Observe action options.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>"Leave" option with exit icon should be visible in orange/red color.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>GA_016</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Verify Leave click shows confirmation</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Click on "Leave".
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Confirmation dialog should appear asking to confirm leaving group.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>GA_017</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>User is logged in and confirmation shown</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Verify Leave confirmation removes user from group</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. Click Leave.
 2. Confirm leaving.
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>User should be removed from group; group should disappear from user's list.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>GA_019</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Verify Delete and Exit action</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>User is logged in and Group Info is open</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Verify Delete and Exit option is visible</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Observe action options.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>"Delete and Exit" option with trash icon should be visible in red color.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>GA_020</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Verify Delete and Exit click shows confirmation</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Click on "Delete and Exit".
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Confirmation dialog should appear warning about permanent deletion.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>GA_021</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>User is owner and confirmation shown</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Verify Delete and Exit deletes group completely</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>1. Click Delete and Exit.
 2. Confirm deletion.
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Group should be permanently deleted for all members.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>GA_023</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Verify View Members tab</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>User is logged in and Group Info is open</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Verify View Members tab is visible</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Observe tabs section.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>"View Members" tab should be visible and selected by default.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>GA_024</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Verify View Members tab shows member list</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Click View Members tab.
 3. Observe list.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>List of group members should display with profile pictures and names.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>GA_025</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>User is logged in and View Members is active</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Verify member profile picture display</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>1. View Members tab is active.
 2. Observe member avatars.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Each member should show profile picture or default avatar.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>GA_026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Verify member name display</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>1. View Members tab is active.
 2. Observe member names.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Member names should display (e.g., "Nancy Grace", "John Paul", "George Alan").</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>GA_027</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Verify owner badge display</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>1. View Members tab is active.
 2. Find group owner in list.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Owner should have "Owner" badge displayed (purple badge).</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>GA_028</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Verify online status indicator</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>1. View Members tab is active.
 2. Observe online indicators.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Green dot should indicate online members.</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>GA_029</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Verify Banned Members tab</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>User is logged in and Group Info is open</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Verify Banned Members tab is visible</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Observe tabs section.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>"Banned Members" tab should be visible next to View Members.</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>GA_030</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Verify Banned Members tab click</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Click Banned Members tab.
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Banned Members tab should become active; list of banned users should display.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>GA_031</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>User is admin and Banned Members is active</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Verify unban option for banned members</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>1. Click Banned Members tab.
 2. Find banned user.
 3. Observe options.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>Unban option should be available for each banned member.</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>GA_033</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Verify Search in members</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>User is logged in and View Members is active</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Verify search field is visible</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. View Members tab is active.
 3. Observe search field.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>Search field should be visible with placeholder "Search".</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>GA_034</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>Verify search by member name</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>1. View Members tab is active.
 2. Type "Nancy" in search field.
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>"Nancy Grace" should appear in filtered results.</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>GA_035</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>Verify search clears correctly</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>1. Type search query.
 2. Clear search field.
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>Full member list should be restored.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>GA_037</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Verify Kick action</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>User is admin and View Members is active</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>Verify Kick option in member dropdown</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>1. View Members tab is active.
 2. Click dropdown on a member.
 3. Observe options.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>"Kick" option should be visible in dropdown menu.</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>GA_038</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>Verify Kick click shows confirmation</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>1. Click dropdown on a member.
 2. Click "Kick".
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>Confirmation dialog should appear asking to confirm kick.</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>GA_039</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>User is admin and confirmation shown</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Verify Kick removes member from group</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>1. Click Kick.
 2. Confirm action.
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>Member should be removed from group; member count should decrease.</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>GA_042</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>Verify Ban action</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>User is admin and View Members is active</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>Verify Ban option in member dropdown</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>1. View Members tab is active.
 2. Click dropdown on a member.
 3. Observe options.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>"Ban" option should be visible in dropdown menu.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>GA_043</t>
         </is>
       </c>
-      <c r="B35" s="2" t="n"/>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>Verify Ban click shows confirmation</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>1. Click dropdown on a member.
 2. Click "Ban".
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>Confirmation dialog should appear asking to confirm ban.</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>GA_044</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>User is admin and confirmation shown</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>Verify Ban removes and blocks member</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>1. Click Ban.
 2. Confirm action.
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>Member should be removed and added to Banned Members list.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>GA_047</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>Verify Change Scope action</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>User is admin and View Members is active</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>Verify Change Scope option in member dropdown</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>1. View Members tab is active.
 2. Click dropdown on a member.
 3. Observe options.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
         <is>
           <t>"Change Scope" option should be visible in dropdown menu.</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>GA_048</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>Verify Change Scope click opens options</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>1. Click dropdown on a member.
 2. Click "Change Scope".
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>Scope options should appear (e.g., Admin, Moderator, Member).</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>GA_049</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n"/>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>User is admin and scope options shown</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>Verify promoting member to admin</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>1. Click Change Scope.
 2. Select "Admin".
 3. Confirm action.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>Member's role should change to Admin.</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>GA_050</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n"/>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>Verify demoting admin to member</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>1. Click Change Scope on admin.
 2. Select "Member".
 3. Confirm action.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>Admin's role should change to Member.</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>GA_053</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>Verify UI responsiveness</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>Verify Group Info panel on desktop</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>1. Open application on desktop.
 2. Open Group Info panel.
 3. Resize browser.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>Panel should adjust dynamically; all elements should remain functional.</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>GA_054</t>
         </is>
       </c>
-      <c r="B42" s="2" t="n"/>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>Verify Group Info panel on mobile</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>1. Open application on mobile.
 2. Open Group Info panel.
 3. Check layout.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
         <is>
           <t>Panel should fit screen properly; scrolling should work for long lists.</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n"/>
-      <c r="B43" s="2" t="n"/>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n"/>
-      <c r="E43" s="2" t="n"/>
-      <c r="F43" s="2" t="n"/>
-      <c r="G43" s="2" t="n"/>
-      <c r="H43" s="2" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>GA_009</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Verify Add Members action</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, no users available to add</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Verify empty state when no users to add</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>1. Open Add Members dialog.
-2. Observe when all users are already members.</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Empty state message should display (e.g., "No users available to add").</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>GA_010</t>
         </is>
       </c>
-      <c r="B45" s="2" t="n"/>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>User is non-admin member</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>Verify Add Members not available for non-admin</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>1. Login as non-admin member.
 2. Open Group Info panel.
 3. Observe Add Members option.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>Add Members option should be hidden or disabled for non-admin users.</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>GA_041</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>User is admin viewing owner</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Verify cannot kick group owner</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>1. Login as admin.
+2. View Members tab.
+3. Click dropdown on owner.</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>Kick option should not be available for group owner.</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>GA_046</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>User is admin viewing owner</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Verify cannot ban group owner</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>1. Login as admin.
+2. View Members tab.
+3. Click dropdown on owner.</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>Ban option should not be available for group owner.</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>GA_052</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>User is admin viewing owner</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Verify cannot change owner's scope</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>1. Login as admin.
+2. View Members tab.
+3. Click dropdown on owner.</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>Change Scope option should not be available for group owner.</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>GA_080</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Transfer Ownership</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Logged in as group owner</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Verify transfer ownership option available</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>1. Open group details
+2. Check for transfer ownership</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>Transfer ownership option visible for owner</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>GA_081</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Transfer Ownership</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Transfer dialog open</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Verify ownership transfers to selected member</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>1. Click transfer ownership
+2. Select member
+3. Confirm</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>Ownership transferred, new owner has full permissions</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>GA_082</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Transfer Ownership Confirmation</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Transfer initiated</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Verify confirmation toast after transfer</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>1. Complete ownership transfer</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>Success toast: 'Ownership transferred successfully'</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>GA_083</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Unban Member</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Banned members exist</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Verify unban option in banned members list</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>1. Open banned members
+2. Check for unban option</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>Unban option visible for each banned member</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>GA_084</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Unban Member Action</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Unban clicked</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Verify member unbanned successfully</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>1. Click unban on banned member
+2. Confirm</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>Member unbanned, removed from banned list</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>GA_085</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Unban Notification</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>Member unbanned</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Verify unban event notification</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>1. Unban a member</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>Toast: 'Member unbanned' shown</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>GA_086</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Moderator Scope</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Admin logged in</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Verify can change member scope to moderator</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>1. Open member options
+2. Click change scope
+3. Select moderator</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>Member scope changed to moderator</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>GA_087</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Moderator Permissions</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Member is moderator</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Verify moderator can kick/ban participants</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>1. Login as moderator
+2. Check member options</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>Moderator can kick and ban participants</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>GA_088</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Scope Change Dialog</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Change scope clicked</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Verify scope change dialog with options</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>1. Click change scope on member</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>Dialog shows available scopes (admin/moderator/participant)</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>GA_089</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Admin Scope</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Owner logged in</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Verify can promote member to admin</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>1. Change scope
+2. Select admin</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>Member promoted to admin with admin permissions</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="57"/>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>GA_009</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Verify Add Members action</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>User is logged in, no users available to add</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Verify empty state when no users to add</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>1. Open Add Members dialog.
+2. Observe when all users are already members.</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Empty state message should display (e.g., "No users available to add").</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>GA_014</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>Verify Delete Chat action</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>User is logged in, Delete Chat is disabled</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>Verify Delete Chat disabled state</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F59" s="4" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Observe Delete Chat option when disabled.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G59" s="4" t="inlineStr">
         <is>
           <t>Delete Chat should appear grayed out and not clickable.</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H59" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>GA_018</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>Verify Leave action</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>User is group owner</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>Verify owner cannot leave without transferring ownership</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>1. Login as group owner.
 2. Open Group Info.
 3. Click Leave.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>Warning should display that owner must transfer ownership or delete group.</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H60" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>GA_022</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>Verify Delete and Exit action</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>User is non-owner member</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>Verify Delete and Exit not available for non-owner</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>1. Login as non-owner member.
 2. Open Group Info panel.
 3. Observe Delete and Exit option.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G61" s="4" t="inlineStr">
         <is>
           <t>Delete and Exit option should be hidden or disabled for non-owner users.</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H61" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>GA_032</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>Verify Banned Members tab</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>User is logged in, no banned members</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>Verify empty Banned Members state</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>1. Click Banned Members tab.
 2. Observe when no users are banned.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G62" s="4" t="inlineStr">
         <is>
           <t>Empty state message should display (e.g., "No banned members").</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H62" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>GA_036</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>Verify Search in members</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>User is logged in and View Members is active</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E63" s="4" t="inlineStr">
         <is>
           <t>Verify search with no results</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F63" s="4" t="inlineStr">
         <is>
           <t>1. Type "XYZ123" in search field.
 2. Observe results.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G63" s="4" t="inlineStr">
         <is>
           <t>Empty state should display (e.g., "No members found").</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H63" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>GA_040</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>Verify Kick action</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>User is non-admin member</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>Verify Kick not available for non-admin</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>1. Login as non-admin.
 2. View Members tab.
 3. Observe member options.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t>Kick option should not be visible for non-admin users.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H64" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>GA_041</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n"/>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>User is admin viewing owner</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Verify cannot kick group owner</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>1. Login as admin.
-2. View Members tab.
-3. Click dropdown on owner.</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>Kick option should not be available for group owner.</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>GA_045</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>Verify Ban action</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>User is non-admin member</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>Verify Ban not available for non-admin</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>1. Login as non-admin.
 2. View Members tab.
 3. Observe member options.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G65" s="4" t="inlineStr">
         <is>
           <t>Ban option should not be visible for non-admin users.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H65" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>GA_046</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>User is admin viewing owner</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Verify cannot ban group owner</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>1. Login as admin.
-2. View Members tab.
-3. Click dropdown on owner.</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Ban option should not be available for group owner.</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>GA_051</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>Verify Change Scope action</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>User is non-admin member</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr">
         <is>
           <t>Verify Change Scope not available for non-admin</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F66" s="4" t="inlineStr">
         <is>
           <t>1. Login as non-admin.
 2. View Members tab.
 3. Observe member options.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G66" s="4" t="inlineStr">
         <is>
           <t>Change Scope option should not be visible for non-admin users.</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H66" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>GA_052</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="n"/>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>User is admin viewing owner</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Verify cannot change owner's scope</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>1. Login as admin.
-2. View Members tab.
-3. Click dropdown on owner.</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Change Scope option should not be available for group owner.</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>GA_090</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Transfer Ownership - Non-Owner</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Logged in as admin (not owner)</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Verify transfer ownership not available for non-owner</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>1. Login as admin
+2. Check group options</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>Transfer ownership option not visible</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>GA_091</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Unban - No Permission</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Logged in as participant</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Verify participant cannot unban members</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>1. Login as participant
+2. Try to access banned members</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>Banned members/unban not accessible</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>GA_092</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Scope Change - Participant</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Logged in as participant</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Verify participant cannot change scopes</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>1. Login as participant
+2. Check member options</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>Change scope option not visible</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>GA_093</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Transfer to Self</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Owner tries to transfer to self</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Verify cannot transfer ownership to self</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>1. Try to select self in transfer dialog</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>Self not shown or disabled in transfer list</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>GA_094</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Moderator Scope Change on Admin</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Moderator tries to change admin scope</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Verify moderator cannot change admin's scope</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>1. Login as moderator
+2. Check admin's options</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>Change scope not available for admins</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2532,206 +3188,379 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="0070AD47"/>
+    <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>GA_055</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Integration: Group Actions with Message List</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and group is open</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify adding member shows system message in chat</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Add a new member to the group.
 2. Observe message list.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>System message 'User X was added' should appear in the group chat.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>GA_056</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify kicking member shows system message in chat</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Kick a member from the group.
 2. Observe message list.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>System message 'User X was removed' should appear in the group chat.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GA_057</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Integration: Group Actions with Conversation List</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify leaving group removes it from conversation list</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Leave a group.
 2. Check conversation list.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Group should be removed from conversation list (or marked as 'Left').</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GA_058</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Integration: Group Actions with Notifications</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify group action triggers notification for affected members</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Admin changes a member's scope.
 2. Check affected member's notifications.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Affected member should receive notification about scope change.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>GA_095</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Transfer + Member List Update</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Ownership transferred</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify member list reflects new ownership</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Transfer ownership
+2. Check member list</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>New owner shown with owner badge, old owner as admin</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>GA_096</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Unban + Rejoin</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Member unbanned</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify unbanned member can rejoin group</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Unban member
+2. Member tries to join</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Unbanned member can join group again</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>GA_097</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Scope Change + Permissions</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Scope changed to moderator</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify permissions update immediately</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. Change scope to moderator
+2. Check permissions</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>New moderator permissions active immediately</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>GA_098</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Transfer + Offline</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Network disconnected</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Verify transfer fails gracefully offline</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. Disconnect network
+2. Try transfer</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Error message shown, ownership unchanged</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2743,168 +3572,298 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00FFC000"/>
+    <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>GA_059</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Regression: Group Actions</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and is group admin</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify group actions work after adding and removing same member</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Add User X.
 2. Remove User X.
 3. Add User X again.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>All actions should complete successfully. User X should be a member again.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>GA_060</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify group actions after scope change</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Change User X from member to admin.
 2. Perform admin actions as User X.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>User X should have full admin capabilities after scope change.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GA_061</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify member list accurate after multiple actions</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Add 3 members, remove 1, ban 1.
 2. View member list.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Member list should accurately reflect all changes. Counts should be correct.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>GA_099</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Transfer After Member Leave</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Members left group</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verify transfer works with remaining members</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. Some members leave
+2. Transfer ownership</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Transfer works with available members</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>GA_100</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Unban After Re-ban</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Member banned again after unban</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify re-ban works after unban</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Unban member
+2. Ban again</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Member banned again successfully</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>GA_101</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Scope After Group Delete</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Group deleted</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify scope changes not possible on deleted group</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. Delete group
+2. Try scope change</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Appropriate error handling</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2916,266 +3875,351 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00FF0000"/>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>GA_063</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Verify non-admin cannot kick members</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. Login as regular group member.
+2. Try to kick another member.</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Kick option should not be available or action should be rejected.</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>GA_064</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Verify non-admin cannot ban members</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. Login as regular group member.
+2. Try to ban another member.</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Ban option should not be available or action should be rejected.</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>GA_065</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Verify non-admin cannot change member scope</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. Login as regular group member.
+2. Try to change another member's scope.</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Change scope option should not be available or action should be rejected.</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>GA_066</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>User is logged in as group admin</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verify admin cannot kick/ban the group owner</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. As admin, try to kick or ban the group owner.</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Action should be blocked. Owner cannot be kicked or banned by admin.</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>GA_067</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>User is not a group member</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify non-member cannot access group actions</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Try to access group actions for a group you're not a member of.</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Group actions should not be accessible. Appropriate error should display.</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>GA_102</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Transfer Auth Check</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Valid owner session</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify only authenticated owner can transfer</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Verify auth token for transfer</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Transfer requires valid owner authentication</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>GA_062</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Security: Group Actions</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>User is logged in as regular member</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Verify non-admin cannot add members</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. Login as regular group member.
 2. Try to add a new member.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Add member option should not be available or action should be rejected.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>GA_063</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Verify non-admin cannot kick members</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>1. Login as regular group member.
-2. Try to kick another member.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Kick option should not be available or action should be rejected.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>GA_064</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Verify non-admin cannot ban members</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1. Login as regular group member.
-2. Try to ban another member.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Ban option should not be available or action should be rejected.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>GA_065</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Verify non-admin cannot change member scope</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1. Login as regular group member.
-2. Try to change another member's scope.</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Change scope option should not be available or action should be rejected.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>GA_066</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in as group admin</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Verify admin cannot kick/ban the group owner</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1. As admin, try to kick or ban the group owner.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Action should be blocked. Owner cannot be kicked or banned by admin.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>GA_067</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>User is not a group member</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Verify non-member cannot access group actions</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1. Try to access group actions for a group you're not a member of.</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Group actions should not be accessible. Appropriate error should display.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>GA_103</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Scope Escalation</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Participant tries to self-promote</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Verify cannot escalate own scope via API</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. Attempt self scope change via API</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Permission denied, scope unchanged</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -3191,242 +4235,359 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>GA_068</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Edge Case: Group Actions</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and is group admin</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify adding member to group at max member limit</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Fill group to maximum member limit.
 2. Try to add one more member.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Should show error that group is full. Member should not be added.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>GA_069</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify banning all members except owner</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Ban all members one by one (except owner).</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>All members should be banned. Group should still function with owner only.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GA_070</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify unbanning a previously banned member</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Ban a member.
 2. Go to banned members list.
 3. Unban the member.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Member should be unbanned and able to rejoin the group.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GA_071</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify group actions with 500+ members</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Open group actions for a group with 500+ members.
 2. View member list.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Member list should load with pagination. Search should work. No performance issues.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>GA_104</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Transfer in 2-Member Group</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Group with only 2 members</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify transfer works in minimal group</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Transfer ownership in 2-member group</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Ownership transferred to only other member</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>GA_105</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Unban All Members</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Multiple banned members</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify unbanning all members works</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Unban all banned members one by one</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>All members unbanned, banned list empty</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>GA_072</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Edge Case: Group Actions</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Verify simultaneous admin actions on same member</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. Two admins try to kick the same member at the same time.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>One action should succeed, the other should fail gracefully. No data corruption.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>GA_106</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Transfer Last Admin</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Only one admin/owner</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Verify handling when transferring from sole admin</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. Transfer ownership as sole admin</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Ownership transfers, old owner becomes admin/participant</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -3442,162 +4603,247 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>GA_073</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Boundary: Group Actions</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and is group admin</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify group with exactly 2 members (minimum for group)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Have a group with exactly 2 members.
 2. Perform group actions.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>All applicable actions should work. Leaving should handle last-member scenario.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>GA_074</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify group with maximum allowed members</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Fill group to max capacity.
 2. Verify all actions work.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>All group actions should function correctly at max capacity.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GA_075</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify banned members list with 0 banned members</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Open banned members list when no one is banned.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Empty state should display with appropriate message.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>GA_107</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Scope Options - All Available</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Owner viewing participant</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verify all scope options shown</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. Owner clicks change scope on participant</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Admin, Moderator, Participant options shown</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>GA_108</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Scope Options - Limited</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Admin viewing another admin</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify limited scope options</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Admin clicks change scope on admin</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Only available downgrade options shown</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -3613,194 +4859,363 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>GA_076</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Member Scopes</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and is group owner</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify actions available for Owner scope</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Login as group owner.
 2. Observe available group actions.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Owner should have all actions: add, kick, ban, change scope, delete group.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>GA_077</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify actions available for Admin scope</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Login as group admin.
 2. Observe available group actions.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Admin should have: add, kick (members only), ban (members only), change scope (members only).</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GA_078</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify actions available for Moderator scope</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Login as group moderator.
 2. Observe available group actions.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Moderator should have limited actions per role definition.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GA_079</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify actions available for Member scope</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Login as regular group member.
 2. Observe available group actions.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Member should only have: leave group, view members. No admin actions.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>GA_109</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Owner Actions</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Logged in as owner</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify owner has all group actions</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Check available actions as owner</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Transfer, kick, ban, scope change, delete all available</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>GA_110</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Admin Actions</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Logged in as admin</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify admin has limited actions</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Check available actions as admin</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Kick, ban, scope change available (no transfer/delete)</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>GA_111</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Moderator Actions</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Logged in as moderator</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify moderator has basic actions</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. Check available actions as moderator</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Kick, ban participants available</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>GA_112</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Participant Actions</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Logged in as participant</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Verify participant has no management actions</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. Check available actions as participant</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>No kick/ban/scope change options</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>

--- a/Group_Actions/Group_Actions_Test_Cases.xlsx
+++ b/Group_Actions/Group_Actions_Test_Cases.xlsx
@@ -67,7 +67,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -81,11 +81,12 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -99,6 +100,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -521,32 +529,32 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>GA_001</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Verify Group Info panel</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in and group is selected</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Verify Group Info panel opens</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Groups tab.
 2. Select a group.
@@ -554,2629 +562,4621 @@
 4. Observe panel.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Group Info panel should open with group avatar, name, and member count.</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>GA_002</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verify group avatar display in info panel</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Observe group avatar at top.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Group avatar with initials (e.g., "RA") should display in purple circle.</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>GA_003</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify group name display in info panel</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Observe group name.</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Group name (e.g., "RBAC AND SBAC") should display below avatar.</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>GA_004</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Verify member count in info panel</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Observe member count.</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Member count (e.g., "4 Members") should display below group name.</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>GA_005</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Verify close button (X) functionality</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Click X button in top right.
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Group Info panel should close.</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>GA_006</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Verify Add Members action</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>User is logged in and Group Info is open</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Verify Add Members option is visible</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Observe action options.</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>"Add Members" option with person+ icon should be visible.</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>GA_007</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Verify Add Members click opens dialog</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Click on "Add Members".
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Add Members dialog/screen should open with user selection list.</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>GA_008</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>User is logged in and Add Members dialog is open</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Verify adding a new member to group</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>1. Open Add Members dialog.
 2. Select a user.
 3. Confirm addition.</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Selected user should be added to group; member count should increase.</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>GA_011</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Verify Delete Chat action</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>User is logged in and Group Info is open</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Verify Delete Chat option is visible</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Observe action options.</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>"Delete Chat" option with trash icon should be visible (grayed out if disabled).</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>GA_012</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Verify Delete Chat click shows confirmation</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Click on "Delete Chat".
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Confirmation dialog should appear asking to confirm deletion.</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>GA_013</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>User is logged in and confirmation shown</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Verify Delete Chat confirmation deletes messages</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>1. Click Delete Chat.
 2. Confirm deletion.
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Chat messages should be deleted; group should remain with empty chat.</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>GA_015</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Verify Leave action</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>User is logged in and Group Info is open</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Verify Leave option is visible</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Observe action options.</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>"Leave" option with exit icon should be visible in orange/red color.</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>GA_016</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Verify Leave click shows confirmation</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Click on "Leave".
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Confirmation dialog should appear asking to confirm leaving group.</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>GA_017</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>User is logged in and confirmation shown</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Verify Leave confirmation removes user from group</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>1. Click Leave.
 2. Confirm leaving.
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>User should be removed from group; group should disappear from user's list.</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>GA_019</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Verify Delete and Exit action</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>User is logged in and Group Info is open</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Verify Delete and Exit option is visible</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Observe action options.</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>"Delete and Exit" option with trash icon should be visible in red color.</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>GA_020</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Verify Delete and Exit click shows confirmation</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Click on "Delete and Exit".
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Confirmation dialog should appear warning about permanent deletion.</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>GA_021</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>User is owner and confirmation shown</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Verify Delete and Exit deletes group completely</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>1. Click Delete and Exit.
 2. Confirm deletion.
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Group should be permanently deleted for all members.</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>GA_023</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Verify View Members tab</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>User is logged in and Group Info is open</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Verify View Members tab is visible</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Observe tabs section.</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>"View Members" tab should be visible and selected by default.</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>GA_024</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Verify View Members tab shows member list</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Click View Members tab.
 3. Observe list.</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>List of group members should display with profile pictures and names.</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>GA_025</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>User is logged in and View Members is active</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Verify member profile picture display</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>1. View Members tab is active.
 2. Observe member avatars.</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Each member should show profile picture or default avatar.</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>GA_026</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Verify member name display</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>1. View Members tab is active.
 2. Observe member names.</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Member names should display (e.g., "Nancy Grace", "John Paul", "George Alan").</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>GA_027</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Verify owner badge display</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>1. View Members tab is active.
 2. Find group owner in list.</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Owner should have "Owner" badge displayed (purple badge).</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>GA_028</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Verify online status indicator</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>1. View Members tab is active.
 2. Observe online indicators.</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Green dot should indicate online members.</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>GA_029</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Verify Banned Members tab</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>User is logged in and Group Info is open</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Verify Banned Members tab is visible</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Observe tabs section.</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>"Banned Members" tab should be visible next to View Members.</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>GA_030</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>Verify Banned Members tab click</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Click Banned Members tab.
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Banned Members tab should become active; list of banned users should display.</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>GA_031</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>User is admin and Banned Members is active</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Verify unban option for banned members</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>1. Click Banned Members tab.
 2. Find banned user.
 3. Observe options.</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>Unban option should be available for each banned member.</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>GA_033</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Verify Search in members</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>User is logged in and View Members is active</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Verify search field is visible</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. View Members tab is active.
 3. Observe search field.</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>Search field should be visible with placeholder "Search".</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>GA_034</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Verify search by member name</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>1. View Members tab is active.
 2. Type "Nancy" in search field.
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>"Nancy Grace" should appear in filtered results.</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>GA_035</t>
         </is>
       </c>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Verify search clears correctly</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>1. Type search query.
 2. Clear search field.
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Full member list should be restored.</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>GA_037</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Verify Kick action</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>User is admin and View Members is active</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Verify Kick option in member dropdown</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>1. View Members tab is active.
 2. Click dropdown on a member.
 3. Observe options.</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>"Kick" option should be visible in dropdown menu.</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>GA_038</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Verify Kick click shows confirmation</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>1. Click dropdown on a member.
 2. Click "Kick".
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Confirmation dialog should appear asking to confirm kick.</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>GA_039</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>User is admin and confirmation shown</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Verify Kick removes member from group</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>1. Click Kick.
 2. Confirm action.
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>Member should be removed from group; member count should decrease.</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>GA_042</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Verify Ban action</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>User is admin and View Members is active</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Verify Ban option in member dropdown</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>1. View Members tab is active.
 2. Click dropdown on a member.
 3. Observe options.</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>"Ban" option should be visible in dropdown menu.</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>GA_043</t>
         </is>
       </c>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Verify Ban click shows confirmation</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>1. Click dropdown on a member.
 2. Click "Ban".
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Confirmation dialog should appear asking to confirm ban.</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>GA_044</t>
         </is>
       </c>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>User is admin and confirmation shown</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>Verify Ban removes and blocks member</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>1. Click Ban.
 2. Confirm action.
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Member should be removed and added to Banned Members list.</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>GA_047</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Verify Change Scope action</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>User is admin and View Members is active</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>Verify Change Scope option in member dropdown</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>1. View Members tab is active.
 2. Click dropdown on a member.
 3. Observe options.</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>"Change Scope" option should be visible in dropdown menu.</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>GA_048</t>
         </is>
       </c>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>Verify Change Scope click opens options</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>1. Click dropdown on a member.
 2. Click "Change Scope".
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>Scope options should appear (e.g., Admin, Moderator, Member).</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>GA_049</t>
         </is>
       </c>
-      <c r="B39" s="4" t="n"/>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>User is admin and scope options shown</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>Verify promoting member to admin</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>1. Click Change Scope.
 2. Select "Admin".
 3. Confirm action.</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>Member's role should change to Admin.</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>GA_050</t>
         </is>
       </c>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>Verify demoting admin to member</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>1. Click Change Scope on admin.
 2. Select "Member".
 3. Confirm action.</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>Admin's role should change to Member.</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>GA_053</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Verify UI responsiveness</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>Verify Group Info panel on desktop</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>1. Open application on desktop.
 2. Open Group Info panel.
 3. Resize browser.</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>Panel should adjust dynamically; all elements should remain functional.</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>GA_054</t>
         </is>
       </c>
-      <c r="B42" s="4" t="n"/>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>Verify Group Info panel on mobile</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>1. Open application on mobile.
 2. Open Group Info panel.
 3. Check layout.</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>Panel should fit screen properly; scrolling should work for long lists.</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>GA_010</t>
         </is>
       </c>
-      <c r="B43" s="4" t="n"/>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>User is non-admin member</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>Verify Add Members not available for non-admin</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>1. Login as non-admin member.
 2. Open Group Info panel.
 3. Observe Add Members option.</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>Add Members option should be hidden or disabled for non-admin users.</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>GA_041</t>
         </is>
       </c>
-      <c r="B44" s="4" t="n"/>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>User is admin viewing owner</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>Verify cannot kick group owner</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>1. Login as admin.
 2. View Members tab.
 3. Click dropdown on owner.</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>Kick option should not be available for group owner.</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>GA_046</t>
         </is>
       </c>
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>User is admin viewing owner</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>Verify cannot ban group owner</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>1. Login as admin.
 2. View Members tab.
 3. Click dropdown on owner.</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>Ban option should not be available for group owner.</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>GA_052</t>
         </is>
       </c>
-      <c r="B46" s="4" t="n"/>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>User is admin viewing owner</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>Verify cannot change owner's scope</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>1. Login as admin.
 2. View Members tab.
 3. Click dropdown on owner.</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>Change Scope option should not be available for group owner.</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>GA_080</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>Transfer Ownership</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>Logged in as group owner</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>Verify transfer ownership option available</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>1. Open group details
 2. Check for transfer ownership</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>Transfer ownership option visible for owner</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>GA_081</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>Transfer Ownership</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>Transfer dialog open</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>Verify ownership transfers to selected member</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>1. Click transfer ownership
 2. Select member
 3. Confirm</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>Ownership transferred, new owner has full permissions</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>GA_082</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>Transfer Ownership Confirmation</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>Transfer initiated</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>Verify confirmation toast after transfer</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>1. Complete ownership transfer</t>
         </is>
       </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>Success toast: 'Ownership transferred successfully'</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>GA_083</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>Unban Member</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>Banned members exist</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>Verify unban option in banned members list</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="F50" s="5" t="inlineStr">
         <is>
           <t>1. Open banned members
 2. Check for unban option</t>
         </is>
       </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>Unban option visible for each banned member</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr">
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>GA_084</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>Unban Member Action</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>Unban clicked</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>Verify member unbanned successfully</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>1. Click unban on banned member
 2. Confirm</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>Member unbanned, removed from banned list</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr">
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>GA_085</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>Unban Notification</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>Member unbanned</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>Verify unban event notification</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>1. Unban a member</t>
         </is>
       </c>
-      <c r="G52" s="4" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>Toast: 'Member unbanned' shown</t>
         </is>
       </c>
-      <c r="H52" s="4" t="inlineStr">
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>GA_086</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>Moderator Scope</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>Admin logged in</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>Verify can change member scope to moderator</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>1. Open member options
 2. Click change scope
 3. Select moderator</t>
         </is>
       </c>
-      <c r="G53" s="4" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>Member scope changed to moderator</t>
         </is>
       </c>
-      <c r="H53" s="4" t="inlineStr">
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>GA_087</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>Moderator Permissions</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>Member is moderator</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>Verify moderator can kick/ban participants</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>1. Login as moderator
 2. Check member options</t>
         </is>
       </c>
-      <c r="G54" s="4" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>Moderator can kick and ban participants</t>
         </is>
       </c>
-      <c r="H54" s="4" t="inlineStr">
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>GA_088</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>Scope Change Dialog</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>Change scope clicked</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>Verify scope change dialog with options</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>1. Click change scope on member</t>
         </is>
       </c>
-      <c r="G55" s="4" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>Dialog shows available scopes (admin/moderator/participant)</t>
         </is>
       </c>
-      <c r="H55" s="4" t="inlineStr">
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>GA_089</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>Admin Scope</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>Owner logged in</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>Verify can promote member to admin</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>1. Change scope
 2. Select admin</t>
         </is>
       </c>
-      <c r="G56" s="4" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>Member promoted to admin with admin permissions</t>
         </is>
       </c>
-      <c r="H56" s="4" t="inlineStr">
+      <c r="H56" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="57"/>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>GA_113</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Group Details - Open Panel</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Group conversation selected</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Verify group details panel opens</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>1. Select a group conversation
+2. Click message header
+3. Observe side panel</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Group details panel should show: group info header, avatar, name, member count</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>GA_114</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Group Details - Member Count Display</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Group details panel open</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>Verify member count is displayed</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>1. Open group details
+2. Observe member count</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>Should show '{count} Members' text below group name</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>GA_115</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Group Details - View Members Tab</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Group details open, admin/owner</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Verify View Members tab shows member list</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>1. Click View Members tab
+2. Observe content</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>CometChatGroupMembers component should render with group members</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>GA_116</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Group Details - Banned Members Tab</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Group details open, admin/owner</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>Verify Banned Members tab shows banned list</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>1. Click Banned Members tab
+2. Observe content</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>CometChatBannedMembers component should render</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>GA_117</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Group Details - Add Members (Admin)</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Group details open, user is admin/owner</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Verify Add Members button visible for admin</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>1. Open group details as admin
+2. Observe action items</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Add Members option should be visible and clickable</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>GA_118</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Group Details - Add Members Dialog</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Admin clicks Add Members</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>Verify add members overlay opens</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>1. Click Add Members
+2. Observe overlay</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>Full-screen add members overlay with user list and back button</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>GA_119</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Group Details - Leave Group (Non-Owner)</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Group details open, user is not owner</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Verify leave group with confirmation</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>1. Click Leave
+2. Observe confirmation dialog
+3. Confirm</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Confirmation dialog shown, user leaves group, side panel closes, toast shown</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>GA_120</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Group Details - Leave Group (Owner) Transfer</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Group details open, user is owner, &gt;1 member</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Verify owner leave triggers transfer ownership</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>1. Click Leave as owner
+2. Observe dialog</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>Transfer ownership confirmation dialog should appear first</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>GA_121</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Group Details - Delete &amp; Exit (Admin)</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Group details open, user is admin/owner</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Verify Delete &amp; Exit with confirmation</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>1. Click Delete &amp; Exit
+2. Confirm in dialog</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>Group deleted, conversation removed, side panel closes, toast shown</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>GA_122</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Group Details - Delete Chat</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Group details open</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>Verify delete group chat</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>1. Click Delete Chat
+2. Confirm in dialog</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>Group conversation deleted, side panel closes</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>GA_123</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Group Details - Close Panel</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Group details open</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Verify closing group details</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>1. Click close icon
+2. Observe behavior</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>Side panel should close</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>GA_124</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Group Details - Real-time Member Count</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Group details open</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>Verify member count updates in real-time</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>1. Open group details
+2. Have another user join/leave the group
+3. Observe count</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>Member count should update automatically via SDK group listeners</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>GA_125</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Group Details - Tabs Hidden for Participant</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Group details open, user is participant</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Verify View/Banned Members tabs hidden for participants</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>1. Open group details as participant
+2. Observe tabs</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>View Members and Banned Members tabs should not be visible</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>GA_126</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Transfer - Open Transfer View</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Owner clicks Leave, &gt;1 member</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>Verify transfer ownership view opens</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>1. Click Leave as group owner
+2. Confirm in dialog
+3. Observe</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>Transfer ownership view should open with group members list</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>GA_127</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Transfer - Radio Button Selection</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Transfer view open</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Verify selecting a member via radio button</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>1. Click radio button next to a member
+2. Observe</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Radio button should be selected, Transfer button should become enabled</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>GA_128</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Transfer - Owner Excluded</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Transfer view open</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Verify current owner not shown in list</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>1. Open transfer view
+2. Look for current owner</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Current owner should not have a radio button (returns empty element)</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>GA_129</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Transfer - Execute Transfer</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Member selected</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Verify successful ownership transfer</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>1. Select a member
+2. Click Transfer button</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Ownership transferred, ccOwnershipChanged event fired, dialog closes</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>GA_130</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Transfer - Cancel Button</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Transfer view open</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Verify cancel button closes view</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>1. Click Cancel button
+2. Observe</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Transfer view should close without transferring</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>GA_131</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Transfer - Button Disabled Initially</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Transfer view just opened</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Verify Transfer button disabled until selection</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>1. Open transfer view
+2. Observe Transfer button</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Transfer button should be disabled until a member is selected</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>GA_132</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Transfer - Member Scope Labels</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Transfer view open</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Verify member scope labels on radio buttons</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>1. Open transfer view
+2. Observe radio button labels</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Each member should show their scope (admin/moderator/participant)</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>GA_133</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Banned - View Banned Members List</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Group details open, Banned Members tab</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Verify banned members list displays</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>1. Click Banned Members tab
+2. Observe list</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>List of banned members should be displayed with unban button per member</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>GA_134</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Banned - Unban Member</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Banned members list displayed</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Verify unbanning a member</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>1. Click unban (X) button on a banned member
+2. Observe</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Member should be removed from banned list, ccGroupMemberUnbanned event fired</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>GA_135</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Banned - Empty State</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>No banned members</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Verify empty state for no banned members</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Banned Members tab with no banned members
+2. Observe</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Empty state with icon and 'No banned members' text</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>GA_136</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Banned - Shimmer Loading</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Banned members loading</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Verify shimmer loading state</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Banned Members tab
+2. Observe loading</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>3 shimmer placeholder items should be shown during loading</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>GA_137</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Banned - Real-time Ban Update</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Banned members tab open</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Verify list updates when member is banned</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>1. Open banned members tab
+2. Ban a member from another device
+3. Observe</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Newly banned member should appear in the list automatically</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>GA_138</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Banned - Real-time Unban Update</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Banned members tab open</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Verify list updates when member is unbanned</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>1. Open banned members tab
+2. Unban a member from another device
+3. Observe</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Unbanned member should be removed from the list automatically</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>GA_139</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Banned - Infinite Scroll</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Many banned members</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Verify pagination on scroll</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>1. Open banned members with 30+ members
+2. Scroll to bottom</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>More banned members should be fetched via fetchNext()</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>GA_140</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Add Members - Open View</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Group details, admin clicks Add Members</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Verify add members view opens</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>1. Click Add Members in group details
+2. Observe overlay</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Full-screen add members overlay with users list and selection</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>GA_141</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Add Members - Multi-Select Users</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Add members view open</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Verify selecting multiple users</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>1. Click checkboxes on multiple users
+2. Observe selection</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Multiple users should be selected, button text updates with count</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>GA_142</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Add Members - Button Text Updates</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Users selected</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Verify button text shows member count</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>1. Select 1 user
+2. Observe button
+3. Select 2 more</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Button should show 'Add Member' for 1, 'Add 3 Members' for 3</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>GA_143</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Add Members - Execute Add</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Users selected</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Verify adding selected members</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>1. Select users
+2. Click Add Members button</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Members added via CometChat.addMembersToGroup(), ccGroupMemberAdded event fired</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>GA_144</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Add Members - Back Button</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Add members view open</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Verify back button closes view</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>1. Click back button
+2. Observe</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Add members overlay should close, return to group details</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>GA_145</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Add Members - Button Disabled Initially</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Add members view just opened</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Verify button disabled with no selection</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>1. Open add members
+2. Observe button state</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Add Members button should be disabled until at least 1 user selected</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>GA_146</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Add Members - Deselect User</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Users selected</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Verify deselecting a user</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>1. Select 3 users
+2. Deselect 1
+3. Observe count</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Count should decrease, button text updates accordingly</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>GA_147</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Add Members - Selected Users Preview</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Users selected</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Verify selected users preview</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>1. Select multiple users
+2. Observe preview area</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Selected users should be shown in preview (showSelectedUsersPreview=true)</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>GA_148</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Alert - Kicked From Group</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>User in group, kicked by admin</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Verify alert popup when kicked</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>1. Be in a group conversation
+2. Get kicked by admin
+3. Observe</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Alert popup should show 'No longer part of group' with 'You have been removed by admin'</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>GA_149</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Alert - Banned From Group</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>User in group, banned by admin</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Verify alert popup when banned</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>1. Be in a group conversation
+2. Get banned by admin
+3. Observe</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Alert popup should show 'No longer part of group' with 'You have been banned by admin'</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>GA_150</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Alert - Understood Button</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Alert popup displayed</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Verify Understood button dismisses alert</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>1. See alert popup
+2. Click Understood
+3. Observe</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Alert should close, selected item cleared, side panel closed</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>GA_009</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>Verify Add Members action</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>User is logged in, no users available to add</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Verify empty state when no users to add</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>1. Open Add Members dialog.
 2. Observe when all users are already members.</t>
         </is>
       </c>
-      <c r="G58" s="4" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>Empty state message should display (e.g., "No users available to add").</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>GA_014</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>Verify Delete Chat action</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Delete Chat is disabled</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Verify Delete Chat disabled state</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>1. Open Group Info panel.
 2. Observe Delete Chat option when disabled.</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>Delete Chat should appear grayed out and not clickable.</t>
         </is>
       </c>
-      <c r="H59" s="4" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>GA_018</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>Verify Leave action</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>User is group owner</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Verify owner cannot leave without transferring ownership</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>1. Login as group owner.
 2. Open Group Info.
 3. Click Leave.</t>
         </is>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>Warning should display that owner must transfer ownership or delete group.</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>GA_022</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>Verify Delete and Exit action</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>User is non-owner member</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Verify Delete and Exit not available for non-owner</t>
         </is>
       </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>1. Login as non-owner member.
 2. Open Group Info panel.
 3. Observe Delete and Exit option.</t>
         </is>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>Delete and Exit option should be hidden or disabled for non-owner users.</t>
         </is>
       </c>
-      <c r="H61" s="4" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>GA_032</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>Verify Banned Members tab</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>User is logged in, no banned members</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Verify empty Banned Members state</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>1. Click Banned Members tab.
 2. Observe when no users are banned.</t>
         </is>
       </c>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>Empty state message should display (e.g., "No banned members").</t>
         </is>
       </c>
-      <c r="H62" s="4" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>GA_036</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>Verify Search in members</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>User is logged in and View Members is active</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Verify search with no results</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>1. Type "XYZ123" in search field.
 2. Observe results.</t>
         </is>
       </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>Empty state should display (e.g., "No members found").</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>GA_040</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
         <is>
           <t>Verify Kick action</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>User is non-admin member</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Verify Kick not available for non-admin</t>
         </is>
       </c>
-      <c r="F64" s="4" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>1. Login as non-admin.
 2. View Members tab.
 3. Observe member options.</t>
         </is>
       </c>
-      <c r="G64" s="4" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>Kick option should not be visible for non-admin users.</t>
         </is>
       </c>
-      <c r="H64" s="4" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>GA_045</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
         <is>
           <t>Verify Ban action</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>User is non-admin member</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Verify Ban not available for non-admin</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>1. Login as non-admin.
 2. View Members tab.
 3. Observe member options.</t>
         </is>
       </c>
-      <c r="G65" s="4" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>Ban option should not be visible for non-admin users.</t>
         </is>
       </c>
-      <c r="H65" s="4" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>GA_051</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
         <is>
           <t>Verify Change Scope action</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>User is non-admin member</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Verify Change Scope not available for non-admin</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>1. Login as non-admin.
 2. View Members tab.
 3. Observe member options.</t>
         </is>
       </c>
-      <c r="G66" s="4" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>Change Scope option should not be visible for non-admin users.</t>
         </is>
       </c>
-      <c r="H66" s="4" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>GA_090</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
         <is>
           <t>Transfer Ownership - Non-Owner</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Logged in as admin (not owner)</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Verify transfer ownership not available for non-owner</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. Login as admin
 2. Check group options</t>
         </is>
       </c>
-      <c r="G67" s="4" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>Transfer ownership option not visible</t>
         </is>
       </c>
-      <c r="H67" s="4" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>GA_091</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
         <is>
           <t>Unban - No Permission</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Logged in as participant</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Verify participant cannot unban members</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. Login as participant
 2. Try to access banned members</t>
         </is>
       </c>
-      <c r="G68" s="4" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>Banned members/unban not accessible</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>GA_092</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>Scope Change - Participant</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Logged in as participant</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Verify participant cannot change scopes</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>1. Login as participant
 2. Check member options</t>
         </is>
       </c>
-      <c r="G69" s="4" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>Change scope option not visible</t>
         </is>
       </c>
-      <c r="H69" s="4" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>GA_093</t>
         </is>
       </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>Transfer to Self</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Owner tries to transfer to self</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Verify cannot transfer ownership to self</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>1. Try to select self in transfer dialog</t>
         </is>
       </c>
-      <c r="G70" s="4" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>Self not shown or disabled in transfer list</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>GA_094</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
         <is>
           <t>Moderator Scope Change on Admin</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Moderator tries to change admin scope</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Verify moderator cannot change admin's scope</t>
         </is>
       </c>
-      <c r="F71" s="4" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. Login as moderator
 2. Check admin's options</t>
         </is>
       </c>
-      <c r="G71" s="4" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>Change scope not available for admins</t>
         </is>
       </c>
-      <c r="H71" s="4" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>GA_151</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Group Details - Add Members Hidden Non-Admin</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Group details open, user is participant</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Verify Add Members not visible for participants</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>1. Open group details as participant
+2. Observe actions</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Add Members option should not be visible</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>GA_152</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Group Details - Delete &amp; Exit Hidden Non-Admin</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Group details open, user is participant</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Verify Delete &amp; Exit not visible for participants</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>1. Open group details as participant
+2. Observe actions</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Delete &amp; Exit option should not be visible</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>GA_153</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Group Details - Leave Hidden Single Owner</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Group details open, owner, only member</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Verify Leave hidden when owner is only member</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>1. Open group details as sole owner
+2. Observe actions</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Leave option should not be visible (membersCount == 1 &amp;&amp; owner)</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>GA_154</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Group Details - Delete Chat Disabled Fresh</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Fresh group chat, no messages</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Verify Delete Chat disabled for fresh group chats</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>1. Open details of group with no messages
+2. Observe Delete Chat</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Delete Chat should be visually disabled</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>GA_155</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Transfer - API Failure</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Member selected, API error</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Verify error handling on transfer failure</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>1. Select member
+2. Click Transfer
+3. Simulate API failure</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Error view should appear, loading should stop, isError set to true</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>GA_156</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Transfer - Loading State</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Transfer in progress</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Verify loading state during transfer</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>1. Select member
+2. Click Transfer
+3. Observe button</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Button should show loading indicator during API call</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>GA_157</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Add Members - Add Failure</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Users selected, API error</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Verify error handling on add failure</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>1. Select users
+2. Click Add
+3. Simulate API failure</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Error view should appear with error message, loading stops</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>GA_158</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Add Members - Loading State</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Add in progress</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Verify loading state during add</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>1. Select users
+2. Click Add
+3. Observe button</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Button should show loading indicator during API call</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -3192,7 +5192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3248,317 +5248,791 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>GA_055</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Integration: Group Actions with Message List</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in and group is open</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Verify adding member shows system message in chat</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1. Add a new member to the group.
 2. Observe message list.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>System message 'User X was added' should appear in the group chat.</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>GA_056</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verify kicking member shows system message in chat</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. Kick a member from the group.
 2. Observe message list.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>System message 'User X was removed' should appear in the group chat.</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>GA_057</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Integration: Group Actions with Conversation List</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify leaving group removes it from conversation list</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. Leave a group.
 2. Check conversation list.</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Group should be removed from conversation list (or marked as 'Left').</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>GA_058</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Integration: Group Actions with Notifications</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Verify group action triggers notification for affected members</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. Admin changes a member's scope.
 2. Check affected member's notifications.</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Affected member should receive notification about scope change.</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>GA_095</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Transfer + Member List Update</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Ownership transferred</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Verify member list reflects new ownership</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. Transfer ownership
 2. Check member list</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>New owner shown with owner badge, old owner as admin</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>GA_096</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Unban + Rejoin</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Member unbanned</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Verify unbanned member can rejoin group</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>1. Unban member
 2. Member tries to join</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Unbanned member can join group again</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>GA_097</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Scope Change + Permissions</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Scope changed to moderator</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Verify permissions update immediately</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>1. Change scope to moderator
 2. Check permissions</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>New moderator permissions active immediately</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>GA_159</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Group Details - Scope Change Listener</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Group details open</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Verify scope change updates UI</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1. Have another admin change logged-in user's scope
+2. Observe details</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Action items should update based on new scope, toast shown</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>GA_160</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Group Details - Member Events Update Count</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Group details open</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Verify all member events update count</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>1. Open group details
+2. Trigger member add/kick/ban/leave/join events</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Member count should update for each event type</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>GA_161</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Group Details - Toast Notifications</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Various group actions performed</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Verify toast messages for group events</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. Perform ownership transfer
+2. Change member scope
+3. Add/ban/unban/kick members</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Appropriate toast messages shown for each action</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>GA_162</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Transfer - Ownership Changed Event</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Transfer successful</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Verify ccOwnershipChanged event</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1. Transfer ownership
+2. Monitor events</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>ccOwnershipChanged should fire with group clone and new owner</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>GA_163</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Transfer - Toast Notification</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Transfer successful</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Verify toast on successful transfer</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1. Transfer ownership
+2. Observe toast</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Toast should show 'Ownership transferred successfully'</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>GA_164</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Banned - Unban Action Message</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Member unbanned</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Verify action message created on unban</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1. Unban a member
+2. Monitor events</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Action message should be created with UNBANNED action, proper sender/receiver</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>GA_165</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Banned - SDK Group Listener</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Banned members tab open</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Verify SDK group listener for ban/unban events</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1. Open banned members
+2. Trigger ban/unban from SDK</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>GroupListener should handle onGroupMemberBanned and onGroupMemberUnbanned</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>GA_166</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Add Members - Member Added Event</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Members added successfully</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Verify ccGroupMemberAdded event</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1. Add members
+2. Monitor events</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>ccGroupMemberAdded should fire with messages, usersAdded, userAddedIn, userAddedBy</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>GA_167</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Add Members - Member Count Update</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Members added</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Verify group member count updates</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1. Add 3 members
+2. Check group member count</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Group membersCount should increase by number of successfully added members</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>GA_168</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Add Members - Toast Notification</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Members added</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Verify toast on member add</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1. Add members
+2. Observe toast</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Toast should show 'Member added' message</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>GA_169</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Alert - State Reset After Dismiss</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Alert dismissed</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Verify state reset after alert dismiss</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1. Get kicked/banned
+2. Click Understood
+3. Check state</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>selectedItem, sideComponent should be reset</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>GA_098</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Transfer + Offline</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Network disconnected</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Verify transfer fails gracefully offline</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect network
 2. Try transfer</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>Error message shown, ownership unchanged</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3576,7 +6050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3632,236 +6106,288 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>GA_059</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Regression: Group Actions</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in and is group admin</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Verify group actions work after adding and removing same member</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1. Add User X.
 2. Remove User X.
 3. Add User X again.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>All actions should complete successfully. User X should be a member again.</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>GA_060</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verify group actions after scope change</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. Change User X from member to admin.
 2. Perform admin actions as User X.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>User X should have full admin capabilities after scope change.</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>GA_061</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify member list accurate after multiple actions</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. Add 3 members, remove 1, ban 1.
 2. View member list.</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Member list should accurately reflect all changes. Counts should be correct.</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>GA_099</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Transfer After Member Leave</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Members left group</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Verify transfer works with remaining members</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. Some members leave
 2. Transfer ownership</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Transfer works with available members</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>GA_100</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Unban After Re-ban</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Member banned again after unban</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Verify re-ban works after unban</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. Unban member
 2. Ban again</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Member banned again successfully</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="7"/>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>GA_170</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Group Details - Owner Change Updates Actions</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Ownership transferred</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Verify action items update after ownership change</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1. Transfer ownership to another member
+2. Observe action items</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Add Members and Delete &amp; Exit should disappear if no longer admin/owner</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>GA_101</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Scope After Group Delete</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Group deleted</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Verify scope changes not possible on deleted group</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>1. Delete group
 2. Try scope change</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Appropriate error handling</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -3879,7 +6405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3935,291 +6461,343 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>GA_063</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Verify non-admin cannot kick members</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1. Login as regular group member.
 2. Try to kick another member.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Kick option should not be available or action should be rejected.</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>GA_064</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verify non-admin cannot ban members</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. Login as regular group member.
 2. Try to ban another member.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Ban option should not be available or action should be rejected.</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>GA_065</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify non-admin cannot change member scope</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. Login as regular group member.
 2. Try to change another member's scope.</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Change scope option should not be available or action should be rejected.</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>GA_066</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>User is logged in as group admin</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Verify admin cannot kick/ban the group owner</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. As admin, try to kick or ban the group owner.</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Action should be blocked. Owner cannot be kicked or banned by admin.</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>GA_067</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>User is not a group member</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Verify non-member cannot access group actions</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. Try to access group actions for a group you're not a member of.</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Group actions should not be accessible. Appropriate error should display.</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>GA_102</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Transfer Auth Check</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Valid owner session</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Verify only authenticated owner can transfer</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>1. Verify auth token for transfer</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Transfer requires valid owner authentication</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
+    <row r="8">
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+    </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>GA_062</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Security: Group Actions</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>User is logged in as regular member</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Verify non-admin cannot add members</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>1. Login as regular group member.
 2. Try to add a new member.</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Add member option should not be available or action should be rejected.</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>GA_103</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Scope Escalation</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Participant tries to self-promote</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Verify cannot escalate own scope via API</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>1. Attempt self scope change via API</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Permission denied, scope unchanged</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>GA_171</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Group Details - Participant Cannot Delete Group</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>User is participant</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Verify participant cannot delete group</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. Open group details as participant
+2. Try to find Delete &amp; Exit</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Delete &amp; Exit should not be available, isAllowed() returns false</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -4235,7 +6813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4291,301 +6869,439 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>GA_068</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Edge Case: Group Actions</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in and is group admin</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Verify adding member to group at max member limit</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1. Fill group to maximum member limit.
 2. Try to add one more member.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Should show error that group is full. Member should not be added.</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>GA_069</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verify banning all members except owner</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. Ban all members one by one (except owner).</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>All members should be banned. Group should still function with owner only.</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>GA_070</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify unbanning a previously banned member</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. Ban a member.
 2. Go to banned members list.
 3. Unban the member.</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Member should be unbanned and able to rejoin the group.</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>GA_071</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Verify group actions with 500+ members</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. Open group actions for a group with 500+ members.
 2. View member list.</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Member list should load with pagination. Search should work. No performance issues.</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>GA_104</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Transfer in 2-Member Group</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Group with only 2 members</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Verify transfer works in minimal group</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. Transfer ownership in 2-member group</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Ownership transferred to only other member</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>GA_105</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Unban All Members</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Multiple banned members</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Verify unbanning all members works</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>1. Unban all banned members one by one</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>All members unbanned, banned list empty</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>GA_172</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Group Details - Kicked While Viewing</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Group details open</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Verify behavior when kicked while viewing details</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1. Open group details
+2. Get kicked by admin from another device</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Alert popup should show 'You have been removed by admin'</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>GA_173</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Group Details - Banned While Viewing</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Group details open</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Verify behavior when banned while viewing details</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>1. Open group details
+2. Get banned by admin from another device</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Alert popup should show 'You have been banned by admin'</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>GA_174</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Add Members - Partial Success</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Adding multiple members, some fail</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Verify partial success handling</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>1. Select users including invalid ones
+2. Click Add</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Successfully added members should be reported, failed ones ignored</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>GA_072</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Edge Case: Group Actions</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Verify simultaneous admin actions on same member</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1. Two admins try to kick the same member at the same time.</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>One action should succeed, the other should fail gracefully. No data corruption.</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>GA_106</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Transfer Last Admin</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Only one admin/owner</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Verify handling when transferring from sole admin</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1. Transfer ownership as sole admin</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Ownership transfers, old owner becomes admin/participant</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4603,7 +7319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4659,189 +7375,284 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>GA_073</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Boundary: Group Actions</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in and is group admin</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Verify group with exactly 2 members (minimum for group)</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1. Have a group with exactly 2 members.
 2. Perform group actions.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>All applicable actions should work. Leaving should handle last-member scenario.</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>GA_074</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verify group with maximum allowed members</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. Fill group to max capacity.
 2. Verify all actions work.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>All group actions should function correctly at max capacity.</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>GA_075</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify banned members list with 0 banned members</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. Open banned members list when no one is banned.</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Empty state should display with appropriate message.</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>GA_107</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Scope Options - All Available</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Owner viewing participant</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Verify all scope options shown</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. Owner clicks change scope on participant</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Admin, Moderator, Participant options shown</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>GA_175</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Group Details - Group with 1 Member</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Single member group</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Verify details for single member group</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1. Open details of group with 1 member
+2. Observe</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Should show '1 Members', Leave may be hidden for owner</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>GA_176</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Add Members - Add Single Member</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>1 user selected</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Verify adding exactly 1 member</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1. Select 1 user
+2. Click Add Member</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Single member should be added, button shows 'Add Member'</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>GA_108</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Scope Options - Limited</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Admin viewing another admin</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Verify limited scope options</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>1. Admin clicks change scope on admin</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Only available downgrade options shown</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4859,7 +7670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4915,305 +7726,433 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>GA_076</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Member Scopes</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in and is group owner</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Verify actions available for Owner scope</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1. Login as group owner.
 2. Observe available group actions.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Owner should have all actions: add, kick, ban, change scope, delete group.</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>GA_077</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verify actions available for Admin scope</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. Login as group admin.
 2. Observe available group actions.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Admin should have: add, kick (members only), ban (members only), change scope (members only).</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>GA_078</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify actions available for Moderator scope</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. Login as group moderator.
 2. Observe available group actions.</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Moderator should have limited actions per role definition.</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>GA_079</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Verify actions available for Member scope</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. Login as regular group member.
 2. Observe available group actions.</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Member should only have: leave group, view members. No admin actions.</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>GA_109</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Owner Actions</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Logged in as owner</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Verify owner has all group actions</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. Check available actions as owner</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Transfer, kick, ban, scope change, delete all available</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>GA_110</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Admin Actions</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Logged in as admin</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Verify admin has limited actions</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>1. Check available actions as admin</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Kick, ban, scope change available (no transfer/delete)</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>GA_111</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Moderator Actions</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Logged in as moderator</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Verify moderator has basic actions</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>1. Check available actions as moderator</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Kick, ban participants available</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>GA_177</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Group Details - Owner Scope Actions</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>User is group owner</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Verify all actions visible for owner</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1. Open details as owner
+2. Observe actions</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Add Members, Delete Chat, Leave, Delete &amp; Exit all visible</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>GA_178</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Group Details - Admin Scope Actions</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>User is group admin</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Verify actions for admin</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>1. Open details as admin
+2. Observe actions</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Add Members, Delete Chat, Leave, Delete &amp; Exit visible</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>GA_179</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Group Details - Participant Scope Actions</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>User is participant</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Verify limited actions for participant</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. Open details as participant
+2. Observe actions</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Only Delete Chat and Leave visible</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>GA_112</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Participant Actions</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Logged in as participant</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Verify participant has no management actions</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1. Check available actions as participant</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>No kick/ban/scope change options</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
